--- a/app/services/langchain/data/meteriality-map.xlsx
+++ b/app/services/langchain/data/meteriality-map.xlsx
@@ -2830,7 +2830,7 @@
     <t>ADA.11.01</t>
   </si>
   <si>
-    <t>Medios and Entretenimiento</t>
+    <t>Medios y Entretenimiento</t>
   </si>
   <si>
     <t>(1) Riesgo de burnout, rotación alta y pérdida de talento por exceso de carga laboral; (2) Deterioro de la reputación y conflictos sindicales.</t>
@@ -7180,7 +7180,7 @@
     <t>ADA.27.01</t>
   </si>
   <si>
-    <t>Metales and Minería</t>
+    <t>Metales y Minería</t>
   </si>
   <si>
     <t>(1) Aumento de costos por impuestos al carbono y exigencias regulatorias. (2) Pérdida de competitividad en mercados con normativas Net Zero.</t>
@@ -7453,7 +7453,7 @@
     <t>ADA.28.01</t>
   </si>
   <si>
-    <t>Petróleo and Gas</t>
+    <t>Petróleo y Gas</t>
   </si>
   <si>
     <t>(1) Pérdida de cuota de mercado ante regulaciones ambientales más estrictas. (2) Riesgo reputacional y pérdida de clientes institucionales por falta de innovación sostenible.</t>
@@ -8567,12 +8567,12 @@
     <font>
       <sz val="11.0"/>
       <color rgb="FF202124"/>
-      <name val="Docs-Roboto"/>
+      <name val="Roboto"/>
     </font>
     <font>
       <sz val="11.0"/>
       <color rgb="FF202124"/>
-      <name val="Roboto"/>
+      <name val="Docs-Roboto"/>
     </font>
   </fonts>
   <fills count="3">
@@ -8934,7 +8934,7 @@
       <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -8976,7 +8976,7 @@
       <c r="A4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -9018,7 +9018,7 @@
       <c r="A5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -9060,7 +9060,7 @@
       <c r="A6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -9102,7 +9102,7 @@
       <c r="A7" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -9144,7 +9144,7 @@
       <c r="A8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -9186,7 +9186,7 @@
       <c r="A9" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="4" t="s">
@@ -9228,7 +9228,7 @@
       <c r="A10" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -9270,7 +9270,7 @@
       <c r="A11" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -9312,7 +9312,7 @@
       <c r="A12" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -9354,7 +9354,7 @@
       <c r="A13" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -9396,7 +9396,7 @@
       <c r="A14" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -9438,7 +9438,7 @@
       <c r="A15" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="4" t="s">
@@ -9480,7 +9480,7 @@
       <c r="A16" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -9522,7 +9522,7 @@
       <c r="A17" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>120</v>
       </c>
       <c r="C17" s="4" t="s">
@@ -9564,7 +9564,7 @@
       <c r="A18" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>120</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -9648,7 +9648,7 @@
       <c r="A20" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>120</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -9690,7 +9690,7 @@
       <c r="A21" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>120</v>
       </c>
       <c r="C21" s="4" t="s">
@@ -9732,7 +9732,7 @@
       <c r="A22" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>120</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -9774,7 +9774,7 @@
       <c r="A23" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>120</v>
       </c>
       <c r="C23" s="4" t="s">
@@ -9816,7 +9816,7 @@
       <c r="A24" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="6" t="s">
         <v>120</v>
       </c>
       <c r="C24" s="4" t="s">
@@ -9858,7 +9858,7 @@
       <c r="A25" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>120</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -9900,7 +9900,7 @@
       <c r="A26" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>120</v>
       </c>
       <c r="C26" s="4" t="s">
@@ -9942,7 +9942,7 @@
       <c r="A27" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="6" t="s">
         <v>120</v>
       </c>
       <c r="C27" s="4" t="s">
@@ -9984,7 +9984,7 @@
       <c r="A28" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="6" t="s">
         <v>120</v>
       </c>
       <c r="C28" s="4" t="s">
@@ -10026,7 +10026,7 @@
       <c r="A29" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="6" t="s">
         <v>120</v>
       </c>
       <c r="C29" s="4" t="s">
@@ -10068,7 +10068,7 @@
       <c r="A30" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="6" t="s">
         <v>120</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -10110,7 +10110,7 @@
       <c r="A31" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>120</v>
       </c>
       <c r="C31" s="4" t="s">
@@ -10152,7 +10152,7 @@
       <c r="A32" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="6" t="s">
         <v>211</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -10194,7 +10194,7 @@
       <c r="A33" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="6" t="s">
         <v>211</v>
       </c>
       <c r="C33" s="4" t="s">
@@ -10236,7 +10236,7 @@
       <c r="A34" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="6" t="s">
         <v>211</v>
       </c>
       <c r="C34" s="4" t="s">
@@ -10278,7 +10278,7 @@
       <c r="A35" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="6" t="s">
         <v>211</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -10320,7 +10320,7 @@
       <c r="A36" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="6" t="s">
         <v>211</v>
       </c>
       <c r="C36" s="4" t="s">
@@ -10362,7 +10362,7 @@
       <c r="A37" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="6" t="s">
         <v>211</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -10404,7 +10404,7 @@
       <c r="A38" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="6" t="s">
         <v>211</v>
       </c>
       <c r="C38" s="4" t="s">
@@ -10446,7 +10446,7 @@
       <c r="A39" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="6" t="s">
         <v>211</v>
       </c>
       <c r="C39" s="4" t="s">
@@ -10488,7 +10488,7 @@
       <c r="A40" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="6" t="s">
         <v>211</v>
       </c>
       <c r="C40" s="4" t="s">
@@ -10530,7 +10530,7 @@
       <c r="A41" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="6" t="s">
         <v>211</v>
       </c>
       <c r="C41" s="4" t="s">
@@ -10572,7 +10572,7 @@
       <c r="A42" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="6" t="s">
         <v>211</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -10614,7 +10614,7 @@
       <c r="A43" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="6" t="s">
         <v>211</v>
       </c>
       <c r="C43" s="4" t="s">
@@ -10656,7 +10656,7 @@
       <c r="A44" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="6" t="s">
         <v>211</v>
       </c>
       <c r="C44" s="4" t="s">
@@ -10698,7 +10698,7 @@
       <c r="A45" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="6" t="s">
         <v>211</v>
       </c>
       <c r="C45" s="4" t="s">
@@ -10740,7 +10740,7 @@
       <c r="A46" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="6" t="s">
         <v>211</v>
       </c>
       <c r="C46" s="4" t="s">
@@ -10782,7 +10782,7 @@
       <c r="A47" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="6" t="s">
         <v>302</v>
       </c>
       <c r="C47" s="4" t="s">
@@ -10824,7 +10824,7 @@
       <c r="A48" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="6" t="s">
         <v>302</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -10866,7 +10866,7 @@
       <c r="A49" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="6" t="s">
         <v>302</v>
       </c>
       <c r="C49" s="4" t="s">
@@ -10908,7 +10908,7 @@
       <c r="A50" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="6" t="s">
         <v>302</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -10950,7 +10950,7 @@
       <c r="A51" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="6" t="s">
         <v>302</v>
       </c>
       <c r="C51" s="4" t="s">
@@ -10992,7 +10992,7 @@
       <c r="A52" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="6" t="s">
         <v>302</v>
       </c>
       <c r="C52" s="4" t="s">
@@ -11034,7 +11034,7 @@
       <c r="A53" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="6" t="s">
         <v>302</v>
       </c>
       <c r="C53" s="4" t="s">
@@ -11076,7 +11076,7 @@
       <c r="A54" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="6" t="s">
         <v>302</v>
       </c>
       <c r="C54" s="4" t="s">
@@ -11118,7 +11118,7 @@
       <c r="A55" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="6" t="s">
         <v>302</v>
       </c>
       <c r="C55" s="4" t="s">
@@ -11160,7 +11160,7 @@
       <c r="A56" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="6" t="s">
         <v>302</v>
       </c>
       <c r="C56" s="4" t="s">
@@ -11202,7 +11202,7 @@
       <c r="A57" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="6" t="s">
         <v>302</v>
       </c>
       <c r="C57" s="4" t="s">
@@ -11244,7 +11244,7 @@
       <c r="A58" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="6" t="s">
         <v>302</v>
       </c>
       <c r="C58" s="4" t="s">
@@ -11286,7 +11286,7 @@
       <c r="A59" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="6" t="s">
         <v>302</v>
       </c>
       <c r="C59" s="4" t="s">
@@ -11328,7 +11328,7 @@
       <c r="A60" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="6" t="s">
         <v>302</v>
       </c>
       <c r="C60" s="4" t="s">
@@ -11370,7 +11370,7 @@
       <c r="A61" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="6" t="s">
         <v>302</v>
       </c>
       <c r="C61" s="4" t="s">
@@ -11412,7 +11412,7 @@
       <c r="A62" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="6" t="s">
         <v>393</v>
       </c>
       <c r="C62" s="4" t="s">
@@ -11454,7 +11454,7 @@
       <c r="A63" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="6" t="s">
         <v>393</v>
       </c>
       <c r="C63" s="4" t="s">
@@ -11496,7 +11496,7 @@
       <c r="A64" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B64" s="6" t="s">
         <v>393</v>
       </c>
       <c r="C64" s="4" t="s">
@@ -11538,7 +11538,7 @@
       <c r="A65" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B65" s="6" t="s">
         <v>393</v>
       </c>
       <c r="C65" s="4" t="s">
@@ -11580,7 +11580,7 @@
       <c r="A66" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B66" s="6" t="s">
         <v>393</v>
       </c>
       <c r="C66" s="4" t="s">
@@ -11622,7 +11622,7 @@
       <c r="A67" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B67" s="6" t="s">
         <v>393</v>
       </c>
       <c r="C67" s="4" t="s">
@@ -11664,7 +11664,7 @@
       <c r="A68" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="5" t="s">
         <v>393</v>
       </c>
       <c r="C68" s="4" t="s">
@@ -11706,7 +11706,7 @@
       <c r="A69" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B69" s="6" t="s">
         <v>393</v>
       </c>
       <c r="C69" s="4" t="s">
@@ -11748,7 +11748,7 @@
       <c r="A70" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B70" s="6" t="s">
         <v>393</v>
       </c>
       <c r="C70" s="4" t="s">
@@ -11790,7 +11790,7 @@
       <c r="A71" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="B71" s="6" t="s">
         <v>393</v>
       </c>
       <c r="C71" s="4" t="s">
@@ -11832,7 +11832,7 @@
       <c r="A72" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B72" s="6" t="s">
         <v>393</v>
       </c>
       <c r="C72" s="4" t="s">
@@ -11874,7 +11874,7 @@
       <c r="A73" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="B73" s="6" t="s">
         <v>393</v>
       </c>
       <c r="C73" s="4" t="s">
@@ -11916,7 +11916,7 @@
       <c r="A74" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="6" t="s">
         <v>393</v>
       </c>
       <c r="C74" s="4" t="s">
@@ -11958,7 +11958,7 @@
       <c r="A75" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="B75" s="5" t="s">
+      <c r="B75" s="6" t="s">
         <v>393</v>
       </c>
       <c r="C75" s="4" t="s">
@@ -12000,7 +12000,7 @@
       <c r="A76" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="6" t="s">
         <v>393</v>
       </c>
       <c r="C76" s="4" t="s">
@@ -12042,7 +12042,7 @@
       <c r="A77" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="B77" s="6" t="s">
         <v>484</v>
       </c>
       <c r="C77" s="4" t="s">
@@ -12084,7 +12084,7 @@
       <c r="A78" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="B78" s="6" t="s">
         <v>484</v>
       </c>
       <c r="C78" s="4" t="s">
@@ -12126,7 +12126,7 @@
       <c r="A79" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="B79" s="6" t="s">
         <v>484</v>
       </c>
       <c r="C79" s="4" t="s">
@@ -12168,7 +12168,7 @@
       <c r="A80" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="B80" s="5" t="s">
+      <c r="B80" s="6" t="s">
         <v>484</v>
       </c>
       <c r="C80" s="4" t="s">
@@ -12210,7 +12210,7 @@
       <c r="A81" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="B81" s="6" t="s">
         <v>484</v>
       </c>
       <c r="C81" s="4" t="s">
@@ -12252,7 +12252,7 @@
       <c r="A82" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="B82" s="6" t="s">
         <v>484</v>
       </c>
       <c r="C82" s="4" t="s">
@@ -12294,7 +12294,7 @@
       <c r="A83" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="B83" s="5" t="s">
+      <c r="B83" s="6" t="s">
         <v>484</v>
       </c>
       <c r="C83" s="4" t="s">
@@ -12336,7 +12336,7 @@
       <c r="A84" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="B84" s="5" t="s">
+      <c r="B84" s="6" t="s">
         <v>484</v>
       </c>
       <c r="C84" s="4" t="s">
@@ -12378,7 +12378,7 @@
       <c r="A85" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="B85" s="5" t="s">
+      <c r="B85" s="6" t="s">
         <v>484</v>
       </c>
       <c r="C85" s="4" t="s">
@@ -12420,7 +12420,7 @@
       <c r="A86" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="B86" s="6" t="s">
         <v>484</v>
       </c>
       <c r="C86" s="4" t="s">
@@ -12462,7 +12462,7 @@
       <c r="A87" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="B87" s="6" t="s">
         <v>484</v>
       </c>
       <c r="C87" s="4" t="s">
@@ -12504,7 +12504,7 @@
       <c r="A88" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="B88" s="6" t="s">
         <v>484</v>
       </c>
       <c r="C88" s="4" t="s">
@@ -12546,7 +12546,7 @@
       <c r="A89" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="B89" s="6" t="s">
         <v>484</v>
       </c>
       <c r="C89" s="4" t="s">
@@ -12588,7 +12588,7 @@
       <c r="A90" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="B90" s="6" t="s">
         <v>484</v>
       </c>
       <c r="C90" s="4" t="s">
@@ -12630,7 +12630,7 @@
       <c r="A91" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="B91" s="6" t="s">
         <v>484</v>
       </c>
       <c r="C91" s="4" t="s">
@@ -12672,7 +12672,7 @@
       <c r="A92" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="B92" s="5" t="s">
+      <c r="B92" s="6" t="s">
         <v>575</v>
       </c>
       <c r="C92" s="4" t="s">
@@ -12714,7 +12714,7 @@
       <c r="A93" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="B93" s="5" t="s">
+      <c r="B93" s="6" t="s">
         <v>575</v>
       </c>
       <c r="C93" s="4" t="s">
@@ -12756,7 +12756,7 @@
       <c r="A94" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="B94" s="5" t="s">
+      <c r="B94" s="6" t="s">
         <v>575</v>
       </c>
       <c r="C94" s="4" t="s">
@@ -12798,7 +12798,7 @@
       <c r="A95" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="B95" s="5" t="s">
+      <c r="B95" s="6" t="s">
         <v>575</v>
       </c>
       <c r="C95" s="4" t="s">
@@ -12840,7 +12840,7 @@
       <c r="A96" s="4" t="s">
         <v>599</v>
       </c>
-      <c r="B96" s="5" t="s">
+      <c r="B96" s="6" t="s">
         <v>575</v>
       </c>
       <c r="C96" s="4" t="s">
@@ -12882,7 +12882,7 @@
       <c r="A97" s="4" t="s">
         <v>605</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="B97" s="6" t="s">
         <v>575</v>
       </c>
       <c r="C97" s="4" t="s">
@@ -12924,7 +12924,7 @@
       <c r="A98" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="B98" s="5" t="s">
+      <c r="B98" s="6" t="s">
         <v>575</v>
       </c>
       <c r="C98" s="4" t="s">
@@ -12966,7 +12966,7 @@
       <c r="A99" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B99" s="6" t="s">
         <v>575</v>
       </c>
       <c r="C99" s="4" t="s">
@@ -13008,7 +13008,7 @@
       <c r="A100" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="B100" s="5" t="s">
+      <c r="B100" s="6" t="s">
         <v>575</v>
       </c>
       <c r="C100" s="4" t="s">
@@ -13050,7 +13050,7 @@
       <c r="A101" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="B101" s="5" t="s">
+      <c r="B101" s="6" t="s">
         <v>575</v>
       </c>
       <c r="C101" s="4" t="s">
@@ -13092,7 +13092,7 @@
       <c r="A102" s="4" t="s">
         <v>635</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="B102" s="6" t="s">
         <v>575</v>
       </c>
       <c r="C102" s="4" t="s">
@@ -13134,7 +13134,7 @@
       <c r="A103" s="4" t="s">
         <v>641</v>
       </c>
-      <c r="B103" s="5" t="s">
+      <c r="B103" s="6" t="s">
         <v>575</v>
       </c>
       <c r="C103" s="4" t="s">
@@ -13176,7 +13176,7 @@
       <c r="A104" s="4" t="s">
         <v>647</v>
       </c>
-      <c r="B104" s="6" t="s">
+      <c r="B104" s="5" t="s">
         <v>575</v>
       </c>
       <c r="C104" s="4" t="s">
@@ -13218,7 +13218,7 @@
       <c r="A105" s="4" t="s">
         <v>653</v>
       </c>
-      <c r="B105" s="5" t="s">
+      <c r="B105" s="6" t="s">
         <v>575</v>
       </c>
       <c r="C105" s="4" t="s">
@@ -13260,7 +13260,7 @@
       <c r="A106" s="4" t="s">
         <v>659</v>
       </c>
-      <c r="B106" s="5" t="s">
+      <c r="B106" s="6" t="s">
         <v>575</v>
       </c>
       <c r="C106" s="4" t="s">
@@ -13302,7 +13302,7 @@
       <c r="A107" s="4" t="s">
         <v>665</v>
       </c>
-      <c r="B107" s="6" t="s">
+      <c r="B107" s="5" t="s">
         <v>666</v>
       </c>
       <c r="C107" s="4" t="s">
@@ -13344,7 +13344,7 @@
       <c r="A108" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="B108" s="6" t="s">
+      <c r="B108" s="5" t="s">
         <v>666</v>
       </c>
       <c r="C108" s="4" t="s">
@@ -13386,7 +13386,7 @@
       <c r="A109" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="B109" s="6" t="s">
+      <c r="B109" s="5" t="s">
         <v>666</v>
       </c>
       <c r="C109" s="4" t="s">
@@ -13428,7 +13428,7 @@
       <c r="A110" s="4" t="s">
         <v>684</v>
       </c>
-      <c r="B110" s="6" t="s">
+      <c r="B110" s="5" t="s">
         <v>666</v>
       </c>
       <c r="C110" s="4" t="s">
@@ -13470,7 +13470,7 @@
       <c r="A111" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="B111" s="6" t="s">
+      <c r="B111" s="5" t="s">
         <v>666</v>
       </c>
       <c r="C111" s="4" t="s">
@@ -13512,7 +13512,7 @@
       <c r="A112" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="B112" s="6" t="s">
+      <c r="B112" s="5" t="s">
         <v>666</v>
       </c>
       <c r="C112" s="4" t="s">
@@ -13554,7 +13554,7 @@
       <c r="A113" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="B113" s="6" t="s">
+      <c r="B113" s="5" t="s">
         <v>666</v>
       </c>
       <c r="C113" s="4" t="s">
@@ -13596,7 +13596,7 @@
       <c r="A114" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="B114" s="6" t="s">
+      <c r="B114" s="5" t="s">
         <v>666</v>
       </c>
       <c r="C114" s="4" t="s">
@@ -13638,7 +13638,7 @@
       <c r="A115" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="B115" s="6" t="s">
+      <c r="B115" s="5" t="s">
         <v>666</v>
       </c>
       <c r="C115" s="4" t="s">
@@ -13680,7 +13680,7 @@
       <c r="A116" s="4" t="s">
         <v>720</v>
       </c>
-      <c r="B116" s="6" t="s">
+      <c r="B116" s="5" t="s">
         <v>666</v>
       </c>
       <c r="C116" s="4" t="s">
@@ -13722,7 +13722,7 @@
       <c r="A117" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="B117" s="6" t="s">
+      <c r="B117" s="5" t="s">
         <v>666</v>
       </c>
       <c r="C117" s="4" t="s">
@@ -13764,7 +13764,7 @@
       <c r="A118" s="4" t="s">
         <v>732</v>
       </c>
-      <c r="B118" s="6" t="s">
+      <c r="B118" s="5" t="s">
         <v>666</v>
       </c>
       <c r="C118" s="4" t="s">
@@ -13806,7 +13806,7 @@
       <c r="A119" s="4" t="s">
         <v>738</v>
       </c>
-      <c r="B119" s="6" t="s">
+      <c r="B119" s="5" t="s">
         <v>666</v>
       </c>
       <c r="C119" s="4" t="s">
@@ -13848,7 +13848,7 @@
       <c r="A120" s="4" t="s">
         <v>744</v>
       </c>
-      <c r="B120" s="6" t="s">
+      <c r="B120" s="5" t="s">
         <v>666</v>
       </c>
       <c r="C120" s="4" t="s">
@@ -13890,7 +13890,7 @@
       <c r="A121" s="4" t="s">
         <v>750</v>
       </c>
-      <c r="B121" s="6" t="s">
+      <c r="B121" s="5" t="s">
         <v>666</v>
       </c>
       <c r="C121" s="4" t="s">
@@ -13932,7 +13932,7 @@
       <c r="A122" s="4" t="s">
         <v>756</v>
       </c>
-      <c r="B122" s="6" t="s">
+      <c r="B122" s="5" t="s">
         <v>757</v>
       </c>
       <c r="C122" s="4" t="s">
@@ -14310,7 +14310,7 @@
       <c r="A131" s="4" t="s">
         <v>811</v>
       </c>
-      <c r="B131" s="6" t="s">
+      <c r="B131" s="5" t="s">
         <v>757</v>
       </c>
       <c r="C131" s="4" t="s">
@@ -14562,7 +14562,7 @@
       <c r="A137" s="4" t="s">
         <v>847</v>
       </c>
-      <c r="B137" s="5" t="s">
+      <c r="B137" s="6" t="s">
         <v>848</v>
       </c>
       <c r="C137" s="4" t="s">
@@ -14604,7 +14604,7 @@
       <c r="A138" s="4" t="s">
         <v>854</v>
       </c>
-      <c r="B138" s="5" t="s">
+      <c r="B138" s="6" t="s">
         <v>848</v>
       </c>
       <c r="C138" s="4" t="s">
@@ -14646,7 +14646,7 @@
       <c r="A139" s="4" t="s">
         <v>860</v>
       </c>
-      <c r="B139" s="5" t="s">
+      <c r="B139" s="6" t="s">
         <v>848</v>
       </c>
       <c r="C139" s="4" t="s">
@@ -14688,7 +14688,7 @@
       <c r="A140" s="4" t="s">
         <v>866</v>
       </c>
-      <c r="B140" s="5" t="s">
+      <c r="B140" s="6" t="s">
         <v>848</v>
       </c>
       <c r="C140" s="4" t="s">
@@ -14730,7 +14730,7 @@
       <c r="A141" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="B141" s="5" t="s">
+      <c r="B141" s="6" t="s">
         <v>848</v>
       </c>
       <c r="C141" s="4" t="s">
@@ -14772,7 +14772,7 @@
       <c r="A142" s="4" t="s">
         <v>878</v>
       </c>
-      <c r="B142" s="5" t="s">
+      <c r="B142" s="6" t="s">
         <v>848</v>
       </c>
       <c r="C142" s="4" t="s">
@@ -14814,7 +14814,7 @@
       <c r="A143" s="4" t="s">
         <v>884</v>
       </c>
-      <c r="B143" s="5" t="s">
+      <c r="B143" s="6" t="s">
         <v>848</v>
       </c>
       <c r="C143" s="4" t="s">
@@ -14856,7 +14856,7 @@
       <c r="A144" s="4" t="s">
         <v>890</v>
       </c>
-      <c r="B144" s="5" t="s">
+      <c r="B144" s="6" t="s">
         <v>848</v>
       </c>
       <c r="C144" s="4" t="s">
@@ -14898,7 +14898,7 @@
       <c r="A145" s="4" t="s">
         <v>896</v>
       </c>
-      <c r="B145" s="5" t="s">
+      <c r="B145" s="6" t="s">
         <v>848</v>
       </c>
       <c r="C145" s="4" t="s">
@@ -14940,7 +14940,7 @@
       <c r="A146" s="4" t="s">
         <v>902</v>
       </c>
-      <c r="B146" s="5" t="s">
+      <c r="B146" s="6" t="s">
         <v>848</v>
       </c>
       <c r="C146" s="4" t="s">
@@ -14982,7 +14982,7 @@
       <c r="A147" s="4" t="s">
         <v>908</v>
       </c>
-      <c r="B147" s="5" t="s">
+      <c r="B147" s="6" t="s">
         <v>848</v>
       </c>
       <c r="C147" s="4" t="s">
@@ -15024,7 +15024,7 @@
       <c r="A148" s="4" t="s">
         <v>914</v>
       </c>
-      <c r="B148" s="5" t="s">
+      <c r="B148" s="6" t="s">
         <v>848</v>
       </c>
       <c r="C148" s="4" t="s">
@@ -15066,7 +15066,7 @@
       <c r="A149" s="4" t="s">
         <v>920</v>
       </c>
-      <c r="B149" s="5" t="s">
+      <c r="B149" s="6" t="s">
         <v>848</v>
       </c>
       <c r="C149" s="4" t="s">
@@ -15108,7 +15108,7 @@
       <c r="A150" s="4" t="s">
         <v>926</v>
       </c>
-      <c r="B150" s="5" t="s">
+      <c r="B150" s="6" t="s">
         <v>848</v>
       </c>
       <c r="C150" s="4" t="s">
@@ -15150,7 +15150,7 @@
       <c r="A151" s="4" t="s">
         <v>932</v>
       </c>
-      <c r="B151" s="5" t="s">
+      <c r="B151" s="6" t="s">
         <v>848</v>
       </c>
       <c r="C151" s="4" t="s">
@@ -15192,7 +15192,7 @@
       <c r="A152" s="4" t="s">
         <v>938</v>
       </c>
-      <c r="B152" s="5" t="s">
+      <c r="B152" s="6" t="s">
         <v>939</v>
       </c>
       <c r="C152" s="4" t="s">
@@ -15234,7 +15234,7 @@
       <c r="A153" s="4" t="s">
         <v>945</v>
       </c>
-      <c r="B153" s="5" t="s">
+      <c r="B153" s="6" t="s">
         <v>939</v>
       </c>
       <c r="C153" s="4" t="s">
@@ -15276,7 +15276,7 @@
       <c r="A154" s="4" t="s">
         <v>951</v>
       </c>
-      <c r="B154" s="5" t="s">
+      <c r="B154" s="6" t="s">
         <v>939</v>
       </c>
       <c r="C154" s="4" t="s">
@@ -15318,7 +15318,7 @@
       <c r="A155" s="4" t="s">
         <v>957</v>
       </c>
-      <c r="B155" s="5" t="s">
+      <c r="B155" s="6" t="s">
         <v>939</v>
       </c>
       <c r="C155" s="4" t="s">
@@ -15360,7 +15360,7 @@
       <c r="A156" s="4" t="s">
         <v>963</v>
       </c>
-      <c r="B156" s="5" t="s">
+      <c r="B156" s="6" t="s">
         <v>939</v>
       </c>
       <c r="C156" s="4" t="s">
@@ -15402,7 +15402,7 @@
       <c r="A157" s="4" t="s">
         <v>969</v>
       </c>
-      <c r="B157" s="5" t="s">
+      <c r="B157" s="6" t="s">
         <v>939</v>
       </c>
       <c r="C157" s="4" t="s">
@@ -15444,7 +15444,7 @@
       <c r="A158" s="4" t="s">
         <v>975</v>
       </c>
-      <c r="B158" s="5" t="s">
+      <c r="B158" s="6" t="s">
         <v>939</v>
       </c>
       <c r="C158" s="4" t="s">
@@ -15486,7 +15486,7 @@
       <c r="A159" s="4" t="s">
         <v>981</v>
       </c>
-      <c r="B159" s="5" t="s">
+      <c r="B159" s="6" t="s">
         <v>939</v>
       </c>
       <c r="C159" s="4" t="s">
@@ -15528,7 +15528,7 @@
       <c r="A160" s="4" t="s">
         <v>987</v>
       </c>
-      <c r="B160" s="5" t="s">
+      <c r="B160" s="6" t="s">
         <v>939</v>
       </c>
       <c r="C160" s="4" t="s">
@@ -15570,7 +15570,7 @@
       <c r="A161" s="4" t="s">
         <v>993</v>
       </c>
-      <c r="B161" s="5" t="s">
+      <c r="B161" s="6" t="s">
         <v>939</v>
       </c>
       <c r="C161" s="4" t="s">
@@ -15612,7 +15612,7 @@
       <c r="A162" s="4" t="s">
         <v>999</v>
       </c>
-      <c r="B162" s="5" t="s">
+      <c r="B162" s="6" t="s">
         <v>939</v>
       </c>
       <c r="C162" s="4" t="s">
@@ -15654,7 +15654,7 @@
       <c r="A163" s="4" t="s">
         <v>1005</v>
       </c>
-      <c r="B163" s="5" t="s">
+      <c r="B163" s="6" t="s">
         <v>939</v>
       </c>
       <c r="C163" s="4" t="s">
@@ -15696,7 +15696,7 @@
       <c r="A164" s="4" t="s">
         <v>1011</v>
       </c>
-      <c r="B164" s="5" t="s">
+      <c r="B164" s="6" t="s">
         <v>939</v>
       </c>
       <c r="C164" s="4" t="s">
@@ -15738,7 +15738,7 @@
       <c r="A165" s="4" t="s">
         <v>1017</v>
       </c>
-      <c r="B165" s="5" t="s">
+      <c r="B165" s="6" t="s">
         <v>939</v>
       </c>
       <c r="C165" s="4" t="s">
@@ -15780,7 +15780,7 @@
       <c r="A166" s="4" t="s">
         <v>1023</v>
       </c>
-      <c r="B166" s="5" t="s">
+      <c r="B166" s="6" t="s">
         <v>939</v>
       </c>
       <c r="C166" s="4" t="s">
@@ -15864,7 +15864,7 @@
       <c r="A168" s="4" t="s">
         <v>1036</v>
       </c>
-      <c r="B168" s="5" t="s">
+      <c r="B168" s="6" t="s">
         <v>1030</v>
       </c>
       <c r="C168" s="4" t="s">
@@ -15906,7 +15906,7 @@
       <c r="A169" s="4" t="s">
         <v>1042</v>
       </c>
-      <c r="B169" s="5" t="s">
+      <c r="B169" s="6" t="s">
         <v>1030</v>
       </c>
       <c r="C169" s="4" t="s">
@@ -15948,7 +15948,7 @@
       <c r="A170" s="4" t="s">
         <v>1048</v>
       </c>
-      <c r="B170" s="5" t="s">
+      <c r="B170" s="6" t="s">
         <v>1030</v>
       </c>
       <c r="C170" s="4" t="s">
@@ -15990,7 +15990,7 @@
       <c r="A171" s="4" t="s">
         <v>1054</v>
       </c>
-      <c r="B171" s="5" t="s">
+      <c r="B171" s="6" t="s">
         <v>1030</v>
       </c>
       <c r="C171" s="4" t="s">
@@ -16032,7 +16032,7 @@
       <c r="A172" s="4" t="s">
         <v>1060</v>
       </c>
-      <c r="B172" s="5" t="s">
+      <c r="B172" s="6" t="s">
         <v>1030</v>
       </c>
       <c r="C172" s="4" t="s">
@@ -16074,7 +16074,7 @@
       <c r="A173" s="4" t="s">
         <v>1066</v>
       </c>
-      <c r="B173" s="5" t="s">
+      <c r="B173" s="6" t="s">
         <v>1030</v>
       </c>
       <c r="C173" s="4" t="s">
@@ -16116,7 +16116,7 @@
       <c r="A174" s="4" t="s">
         <v>1072</v>
       </c>
-      <c r="B174" s="5" t="s">
+      <c r="B174" s="6" t="s">
         <v>1030</v>
       </c>
       <c r="C174" s="4" t="s">
@@ -16158,7 +16158,7 @@
       <c r="A175" s="4" t="s">
         <v>1078</v>
       </c>
-      <c r="B175" s="5" t="s">
+      <c r="B175" s="6" t="s">
         <v>1030</v>
       </c>
       <c r="C175" s="4" t="s">
@@ -16200,7 +16200,7 @@
       <c r="A176" s="4" t="s">
         <v>1084</v>
       </c>
-      <c r="B176" s="5" t="s">
+      <c r="B176" s="6" t="s">
         <v>1030</v>
       </c>
       <c r="C176" s="4" t="s">
@@ -16242,7 +16242,7 @@
       <c r="A177" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="B177" s="5" t="s">
+      <c r="B177" s="6" t="s">
         <v>1030</v>
       </c>
       <c r="C177" s="4" t="s">
@@ -16284,7 +16284,7 @@
       <c r="A178" s="4" t="s">
         <v>1096</v>
       </c>
-      <c r="B178" s="5" t="s">
+      <c r="B178" s="6" t="s">
         <v>1030</v>
       </c>
       <c r="C178" s="4" t="s">
@@ -16326,7 +16326,7 @@
       <c r="A179" s="4" t="s">
         <v>1102</v>
       </c>
-      <c r="B179" s="5" t="s">
+      <c r="B179" s="6" t="s">
         <v>1030</v>
       </c>
       <c r="C179" s="4" t="s">
@@ -16368,7 +16368,7 @@
       <c r="A180" s="4" t="s">
         <v>1108</v>
       </c>
-      <c r="B180" s="5" t="s">
+      <c r="B180" s="6" t="s">
         <v>1030</v>
       </c>
       <c r="C180" s="4" t="s">
@@ -16410,7 +16410,7 @@
       <c r="A181" s="4" t="s">
         <v>1114</v>
       </c>
-      <c r="B181" s="5" t="s">
+      <c r="B181" s="6" t="s">
         <v>1030</v>
       </c>
       <c r="C181" s="4" t="s">
@@ -16452,7 +16452,7 @@
       <c r="A182" s="4" t="s">
         <v>1120</v>
       </c>
-      <c r="B182" s="5" t="s">
+      <c r="B182" s="6" t="s">
         <v>1121</v>
       </c>
       <c r="C182" s="4" t="s">
@@ -16494,7 +16494,7 @@
       <c r="A183" s="4" t="s">
         <v>1127</v>
       </c>
-      <c r="B183" s="5" t="s">
+      <c r="B183" s="6" t="s">
         <v>1121</v>
       </c>
       <c r="C183" s="4" t="s">
@@ -16536,7 +16536,7 @@
       <c r="A184" s="4" t="s">
         <v>1133</v>
       </c>
-      <c r="B184" s="5" t="s">
+      <c r="B184" s="6" t="s">
         <v>1121</v>
       </c>
       <c r="C184" s="4" t="s">
@@ -16578,7 +16578,7 @@
       <c r="A185" s="4" t="s">
         <v>1139</v>
       </c>
-      <c r="B185" s="5" t="s">
+      <c r="B185" s="6" t="s">
         <v>1121</v>
       </c>
       <c r="C185" s="4" t="s">
@@ -16620,7 +16620,7 @@
       <c r="A186" s="4" t="s">
         <v>1145</v>
       </c>
-      <c r="B186" s="5" t="s">
+      <c r="B186" s="6" t="s">
         <v>1121</v>
       </c>
       <c r="C186" s="4" t="s">
@@ -16662,7 +16662,7 @@
       <c r="A187" s="4" t="s">
         <v>1151</v>
       </c>
-      <c r="B187" s="5" t="s">
+      <c r="B187" s="6" t="s">
         <v>1121</v>
       </c>
       <c r="C187" s="4" t="s">
@@ -16704,7 +16704,7 @@
       <c r="A188" s="4" t="s">
         <v>1157</v>
       </c>
-      <c r="B188" s="5" t="s">
+      <c r="B188" s="6" t="s">
         <v>1121</v>
       </c>
       <c r="C188" s="4" t="s">
@@ -16746,7 +16746,7 @@
       <c r="A189" s="4" t="s">
         <v>1163</v>
       </c>
-      <c r="B189" s="5" t="s">
+      <c r="B189" s="6" t="s">
         <v>1121</v>
       </c>
       <c r="C189" s="4" t="s">
@@ -16788,7 +16788,7 @@
       <c r="A190" s="4" t="s">
         <v>1169</v>
       </c>
-      <c r="B190" s="5" t="s">
+      <c r="B190" s="6" t="s">
         <v>1121</v>
       </c>
       <c r="C190" s="4" t="s">
@@ -16830,7 +16830,7 @@
       <c r="A191" s="4" t="s">
         <v>1175</v>
       </c>
-      <c r="B191" s="5" t="s">
+      <c r="B191" s="6" t="s">
         <v>1121</v>
       </c>
       <c r="C191" s="4" t="s">
@@ -16872,7 +16872,7 @@
       <c r="A192" s="4" t="s">
         <v>1181</v>
       </c>
-      <c r="B192" s="5" t="s">
+      <c r="B192" s="6" t="s">
         <v>1121</v>
       </c>
       <c r="C192" s="4" t="s">
@@ -16914,7 +16914,7 @@
       <c r="A193" s="4" t="s">
         <v>1187</v>
       </c>
-      <c r="B193" s="5" t="s">
+      <c r="B193" s="6" t="s">
         <v>1121</v>
       </c>
       <c r="C193" s="4" t="s">
@@ -16956,7 +16956,7 @@
       <c r="A194" s="4" t="s">
         <v>1193</v>
       </c>
-      <c r="B194" s="5" t="s">
+      <c r="B194" s="6" t="s">
         <v>1121</v>
       </c>
       <c r="C194" s="4" t="s">
@@ -16998,7 +16998,7 @@
       <c r="A195" s="4" t="s">
         <v>1199</v>
       </c>
-      <c r="B195" s="5" t="s">
+      <c r="B195" s="6" t="s">
         <v>1121</v>
       </c>
       <c r="C195" s="4" t="s">
@@ -17040,7 +17040,7 @@
       <c r="A196" s="4" t="s">
         <v>1205</v>
       </c>
-      <c r="B196" s="5" t="s">
+      <c r="B196" s="6" t="s">
         <v>1121</v>
       </c>
       <c r="C196" s="4" t="s">
@@ -17082,7 +17082,7 @@
       <c r="A197" s="4" t="s">
         <v>1211</v>
       </c>
-      <c r="B197" s="5" t="s">
+      <c r="B197" s="6" t="s">
         <v>1212</v>
       </c>
       <c r="C197" s="4" t="s">
@@ -17124,7 +17124,7 @@
       <c r="A198" s="4" t="s">
         <v>1218</v>
       </c>
-      <c r="B198" s="5" t="s">
+      <c r="B198" s="6" t="s">
         <v>1212</v>
       </c>
       <c r="C198" s="4" t="s">
@@ -17166,7 +17166,7 @@
       <c r="A199" s="4" t="s">
         <v>1224</v>
       </c>
-      <c r="B199" s="5" t="s">
+      <c r="B199" s="6" t="s">
         <v>1212</v>
       </c>
       <c r="C199" s="4" t="s">
@@ -17208,7 +17208,7 @@
       <c r="A200" s="4" t="s">
         <v>1230</v>
       </c>
-      <c r="B200" s="5" t="s">
+      <c r="B200" s="6" t="s">
         <v>1212</v>
       </c>
       <c r="C200" s="4" t="s">
@@ -17250,7 +17250,7 @@
       <c r="A201" s="4" t="s">
         <v>1236</v>
       </c>
-      <c r="B201" s="5" t="s">
+      <c r="B201" s="6" t="s">
         <v>1212</v>
       </c>
       <c r="C201" s="4" t="s">
@@ -17292,7 +17292,7 @@
       <c r="A202" s="4" t="s">
         <v>1242</v>
       </c>
-      <c r="B202" s="5" t="s">
+      <c r="B202" s="6" t="s">
         <v>1212</v>
       </c>
       <c r="C202" s="4" t="s">
@@ -17334,7 +17334,7 @@
       <c r="A203" s="4" t="s">
         <v>1248</v>
       </c>
-      <c r="B203" s="5" t="s">
+      <c r="B203" s="6" t="s">
         <v>1212</v>
       </c>
       <c r="C203" s="4" t="s">
@@ -17376,7 +17376,7 @@
       <c r="A204" s="4" t="s">
         <v>1254</v>
       </c>
-      <c r="B204" s="5" t="s">
+      <c r="B204" s="6" t="s">
         <v>1212</v>
       </c>
       <c r="C204" s="4" t="s">
@@ -17418,7 +17418,7 @@
       <c r="A205" s="4" t="s">
         <v>1260</v>
       </c>
-      <c r="B205" s="5" t="s">
+      <c r="B205" s="6" t="s">
         <v>1212</v>
       </c>
       <c r="C205" s="4" t="s">
@@ -17460,7 +17460,7 @@
       <c r="A206" s="4" t="s">
         <v>1266</v>
       </c>
-      <c r="B206" s="5" t="s">
+      <c r="B206" s="6" t="s">
         <v>1212</v>
       </c>
       <c r="C206" s="4" t="s">
@@ -17502,7 +17502,7 @@
       <c r="A207" s="4" t="s">
         <v>1272</v>
       </c>
-      <c r="B207" s="5" t="s">
+      <c r="B207" s="6" t="s">
         <v>1212</v>
       </c>
       <c r="C207" s="4" t="s">
@@ -17544,7 +17544,7 @@
       <c r="A208" s="4" t="s">
         <v>1278</v>
       </c>
-      <c r="B208" s="5" t="s">
+      <c r="B208" s="6" t="s">
         <v>1212</v>
       </c>
       <c r="C208" s="4" t="s">
@@ -17586,7 +17586,7 @@
       <c r="A209" s="4" t="s">
         <v>1284</v>
       </c>
-      <c r="B209" s="5" t="s">
+      <c r="B209" s="6" t="s">
         <v>1212</v>
       </c>
       <c r="C209" s="4" t="s">
@@ -17628,7 +17628,7 @@
       <c r="A210" s="4" t="s">
         <v>1290</v>
       </c>
-      <c r="B210" s="5" t="s">
+      <c r="B210" s="6" t="s">
         <v>1212</v>
       </c>
       <c r="C210" s="4" t="s">
@@ -17670,7 +17670,7 @@
       <c r="A211" s="4" t="s">
         <v>1296</v>
       </c>
-      <c r="B211" s="5" t="s">
+      <c r="B211" s="6" t="s">
         <v>1212</v>
       </c>
       <c r="C211" s="4" t="s">
@@ -17712,7 +17712,7 @@
       <c r="A212" s="4" t="s">
         <v>1302</v>
       </c>
-      <c r="B212" s="5" t="s">
+      <c r="B212" s="6" t="s">
         <v>1303</v>
       </c>
       <c r="C212" s="4" t="s">
@@ -17754,7 +17754,7 @@
       <c r="A213" s="4" t="s">
         <v>1309</v>
       </c>
-      <c r="B213" s="5" t="s">
+      <c r="B213" s="6" t="s">
         <v>1303</v>
       </c>
       <c r="C213" s="4" t="s">
@@ -17796,7 +17796,7 @@
       <c r="A214" s="4" t="s">
         <v>1315</v>
       </c>
-      <c r="B214" s="5" t="s">
+      <c r="B214" s="6" t="s">
         <v>1303</v>
       </c>
       <c r="C214" s="4" t="s">
@@ -17838,7 +17838,7 @@
       <c r="A215" s="4" t="s">
         <v>1321</v>
       </c>
-      <c r="B215" s="5" t="s">
+      <c r="B215" s="6" t="s">
         <v>1303</v>
       </c>
       <c r="C215" s="4" t="s">
@@ -17880,7 +17880,7 @@
       <c r="A216" s="4" t="s">
         <v>1327</v>
       </c>
-      <c r="B216" s="5" t="s">
+      <c r="B216" s="6" t="s">
         <v>1303</v>
       </c>
       <c r="C216" s="4" t="s">
@@ -17922,7 +17922,7 @@
       <c r="A217" s="4" t="s">
         <v>1333</v>
       </c>
-      <c r="B217" s="5" t="s">
+      <c r="B217" s="6" t="s">
         <v>1303</v>
       </c>
       <c r="C217" s="4" t="s">
@@ -17964,7 +17964,7 @@
       <c r="A218" s="4" t="s">
         <v>1339</v>
       </c>
-      <c r="B218" s="5" t="s">
+      <c r="B218" s="6" t="s">
         <v>1303</v>
       </c>
       <c r="C218" s="4" t="s">
@@ -18006,7 +18006,7 @@
       <c r="A219" s="4" t="s">
         <v>1345</v>
       </c>
-      <c r="B219" s="5" t="s">
+      <c r="B219" s="6" t="s">
         <v>1303</v>
       </c>
       <c r="C219" s="4" t="s">
@@ -18048,7 +18048,7 @@
       <c r="A220" s="4" t="s">
         <v>1351</v>
       </c>
-      <c r="B220" s="5" t="s">
+      <c r="B220" s="6" t="s">
         <v>1303</v>
       </c>
       <c r="C220" s="4" t="s">
@@ -18090,7 +18090,7 @@
       <c r="A221" s="4" t="s">
         <v>1357</v>
       </c>
-      <c r="B221" s="5" t="s">
+      <c r="B221" s="6" t="s">
         <v>1303</v>
       </c>
       <c r="C221" s="4" t="s">
@@ -18132,7 +18132,7 @@
       <c r="A222" s="4" t="s">
         <v>1363</v>
       </c>
-      <c r="B222" s="5" t="s">
+      <c r="B222" s="6" t="s">
         <v>1303</v>
       </c>
       <c r="C222" s="4" t="s">
@@ -18174,7 +18174,7 @@
       <c r="A223" s="4" t="s">
         <v>1369</v>
       </c>
-      <c r="B223" s="5" t="s">
+      <c r="B223" s="6" t="s">
         <v>1303</v>
       </c>
       <c r="C223" s="4" t="s">
@@ -18216,7 +18216,7 @@
       <c r="A224" s="4" t="s">
         <v>1375</v>
       </c>
-      <c r="B224" s="5" t="s">
+      <c r="B224" s="6" t="s">
         <v>1303</v>
       </c>
       <c r="C224" s="4" t="s">
@@ -18258,7 +18258,7 @@
       <c r="A225" s="4" t="s">
         <v>1381</v>
       </c>
-      <c r="B225" s="5" t="s">
+      <c r="B225" s="6" t="s">
         <v>1303</v>
       </c>
       <c r="C225" s="4" t="s">
@@ -18300,7 +18300,7 @@
       <c r="A226" s="4" t="s">
         <v>1387</v>
       </c>
-      <c r="B226" s="5" t="s">
+      <c r="B226" s="6" t="s">
         <v>1303</v>
       </c>
       <c r="C226" s="4" t="s">
@@ -18342,7 +18342,7 @@
       <c r="A227" s="4" t="s">
         <v>1393</v>
       </c>
-      <c r="B227" s="5" t="s">
+      <c r="B227" s="6" t="s">
         <v>1394</v>
       </c>
       <c r="C227" s="4" t="s">
@@ -18384,7 +18384,7 @@
       <c r="A228" s="4" t="s">
         <v>1400</v>
       </c>
-      <c r="B228" s="5" t="s">
+      <c r="B228" s="6" t="s">
         <v>1394</v>
       </c>
       <c r="C228" s="4" t="s">
@@ -18426,7 +18426,7 @@
       <c r="A229" s="4" t="s">
         <v>1406</v>
       </c>
-      <c r="B229" s="5" t="s">
+      <c r="B229" s="6" t="s">
         <v>1394</v>
       </c>
       <c r="C229" s="4" t="s">
@@ -18468,7 +18468,7 @@
       <c r="A230" s="4" t="s">
         <v>1412</v>
       </c>
-      <c r="B230" s="5" t="s">
+      <c r="B230" s="6" t="s">
         <v>1394</v>
       </c>
       <c r="C230" s="4" t="s">
@@ -18510,7 +18510,7 @@
       <c r="A231" s="4" t="s">
         <v>1418</v>
       </c>
-      <c r="B231" s="5" t="s">
+      <c r="B231" s="6" t="s">
         <v>1394</v>
       </c>
       <c r="C231" s="4" t="s">
@@ -18552,7 +18552,7 @@
       <c r="A232" s="4" t="s">
         <v>1424</v>
       </c>
-      <c r="B232" s="5" t="s">
+      <c r="B232" s="6" t="s">
         <v>1394</v>
       </c>
       <c r="C232" s="4" t="s">
@@ -18594,7 +18594,7 @@
       <c r="A233" s="4" t="s">
         <v>1430</v>
       </c>
-      <c r="B233" s="5" t="s">
+      <c r="B233" s="6" t="s">
         <v>1394</v>
       </c>
       <c r="C233" s="4" t="s">
@@ -18636,7 +18636,7 @@
       <c r="A234" s="4" t="s">
         <v>1436</v>
       </c>
-      <c r="B234" s="5" t="s">
+      <c r="B234" s="6" t="s">
         <v>1394</v>
       </c>
       <c r="C234" s="4" t="s">
@@ -18678,7 +18678,7 @@
       <c r="A235" s="4" t="s">
         <v>1442</v>
       </c>
-      <c r="B235" s="5" t="s">
+      <c r="B235" s="6" t="s">
         <v>1394</v>
       </c>
       <c r="C235" s="4" t="s">
@@ -18720,7 +18720,7 @@
       <c r="A236" s="4" t="s">
         <v>1448</v>
       </c>
-      <c r="B236" s="5" t="s">
+      <c r="B236" s="6" t="s">
         <v>1394</v>
       </c>
       <c r="C236" s="4" t="s">
@@ -18762,7 +18762,7 @@
       <c r="A237" s="4" t="s">
         <v>1454</v>
       </c>
-      <c r="B237" s="5" t="s">
+      <c r="B237" s="6" t="s">
         <v>1394</v>
       </c>
       <c r="C237" s="4" t="s">
@@ -18804,7 +18804,7 @@
       <c r="A238" s="4" t="s">
         <v>1460</v>
       </c>
-      <c r="B238" s="5" t="s">
+      <c r="B238" s="6" t="s">
         <v>1394</v>
       </c>
       <c r="C238" s="4" t="s">
@@ -18846,7 +18846,7 @@
       <c r="A239" s="4" t="s">
         <v>1466</v>
       </c>
-      <c r="B239" s="5" t="s">
+      <c r="B239" s="6" t="s">
         <v>1394</v>
       </c>
       <c r="C239" s="4" t="s">
@@ -18888,7 +18888,7 @@
       <c r="A240" s="4" t="s">
         <v>1472</v>
       </c>
-      <c r="B240" s="5" t="s">
+      <c r="B240" s="6" t="s">
         <v>1394</v>
       </c>
       <c r="C240" s="4" t="s">
@@ -18930,7 +18930,7 @@
       <c r="A241" s="4" t="s">
         <v>1478</v>
       </c>
-      <c r="B241" s="5" t="s">
+      <c r="B241" s="6" t="s">
         <v>1394</v>
       </c>
       <c r="C241" s="4" t="s">
@@ -18972,7 +18972,7 @@
       <c r="A242" s="4" t="s">
         <v>1484</v>
       </c>
-      <c r="B242" s="5" t="s">
+      <c r="B242" s="6" t="s">
         <v>1485</v>
       </c>
       <c r="C242" s="4" t="s">
@@ -19014,7 +19014,7 @@
       <c r="A243" s="4" t="s">
         <v>1491</v>
       </c>
-      <c r="B243" s="5" t="s">
+      <c r="B243" s="6" t="s">
         <v>1485</v>
       </c>
       <c r="C243" s="4" t="s">
@@ -19056,7 +19056,7 @@
       <c r="A244" s="4" t="s">
         <v>1497</v>
       </c>
-      <c r="B244" s="5" t="s">
+      <c r="B244" s="6" t="s">
         <v>1485</v>
       </c>
       <c r="C244" s="4" t="s">
@@ -19098,7 +19098,7 @@
       <c r="A245" s="4" t="s">
         <v>1503</v>
       </c>
-      <c r="B245" s="5" t="s">
+      <c r="B245" s="6" t="s">
         <v>1485</v>
       </c>
       <c r="C245" s="4" t="s">
@@ -19140,7 +19140,7 @@
       <c r="A246" s="4" t="s">
         <v>1509</v>
       </c>
-      <c r="B246" s="5" t="s">
+      <c r="B246" s="6" t="s">
         <v>1485</v>
       </c>
       <c r="C246" s="4" t="s">
@@ -19182,7 +19182,7 @@
       <c r="A247" s="4" t="s">
         <v>1515</v>
       </c>
-      <c r="B247" s="5" t="s">
+      <c r="B247" s="6" t="s">
         <v>1485</v>
       </c>
       <c r="C247" s="4" t="s">
@@ -19224,7 +19224,7 @@
       <c r="A248" s="4" t="s">
         <v>1521</v>
       </c>
-      <c r="B248" s="5" t="s">
+      <c r="B248" s="6" t="s">
         <v>1485</v>
       </c>
       <c r="C248" s="4" t="s">
@@ -19266,7 +19266,7 @@
       <c r="A249" s="4" t="s">
         <v>1527</v>
       </c>
-      <c r="B249" s="5" t="s">
+      <c r="B249" s="6" t="s">
         <v>1485</v>
       </c>
       <c r="C249" s="4" t="s">
@@ -19308,7 +19308,7 @@
       <c r="A250" s="4" t="s">
         <v>1533</v>
       </c>
-      <c r="B250" s="5" t="s">
+      <c r="B250" s="6" t="s">
         <v>1485</v>
       </c>
       <c r="C250" s="4" t="s">
@@ -19350,7 +19350,7 @@
       <c r="A251" s="4" t="s">
         <v>1539</v>
       </c>
-      <c r="B251" s="5" t="s">
+      <c r="B251" s="6" t="s">
         <v>1485</v>
       </c>
       <c r="C251" s="4" t="s">
@@ -19392,7 +19392,7 @@
       <c r="A252" s="4" t="s">
         <v>1545</v>
       </c>
-      <c r="B252" s="5" t="s">
+      <c r="B252" s="6" t="s">
         <v>1485</v>
       </c>
       <c r="C252" s="4" t="s">
@@ -19434,7 +19434,7 @@
       <c r="A253" s="4" t="s">
         <v>1551</v>
       </c>
-      <c r="B253" s="5" t="s">
+      <c r="B253" s="6" t="s">
         <v>1485</v>
       </c>
       <c r="C253" s="4" t="s">
@@ -19476,7 +19476,7 @@
       <c r="A254" s="4" t="s">
         <v>1557</v>
       </c>
-      <c r="B254" s="5" t="s">
+      <c r="B254" s="6" t="s">
         <v>1485</v>
       </c>
       <c r="C254" s="4" t="s">
@@ -19518,7 +19518,7 @@
       <c r="A255" s="4" t="s">
         <v>1563</v>
       </c>
-      <c r="B255" s="5" t="s">
+      <c r="B255" s="6" t="s">
         <v>1485</v>
       </c>
       <c r="C255" s="4" t="s">
@@ -19560,7 +19560,7 @@
       <c r="A256" s="4" t="s">
         <v>1569</v>
       </c>
-      <c r="B256" s="5" t="s">
+      <c r="B256" s="6" t="s">
         <v>1485</v>
       </c>
       <c r="C256" s="4" t="s">
@@ -20232,7 +20232,7 @@
       <c r="A272" s="4" t="s">
         <v>1666</v>
       </c>
-      <c r="B272" s="5" t="s">
+      <c r="B272" s="6" t="s">
         <v>1667</v>
       </c>
       <c r="C272" s="4" t="s">
@@ -20274,7 +20274,7 @@
       <c r="A273" s="4" t="s">
         <v>1673</v>
       </c>
-      <c r="B273" s="5" t="s">
+      <c r="B273" s="6" t="s">
         <v>1667</v>
       </c>
       <c r="C273" s="4" t="s">
@@ -20316,7 +20316,7 @@
       <c r="A274" s="4" t="s">
         <v>1679</v>
       </c>
-      <c r="B274" s="5" t="s">
+      <c r="B274" s="6" t="s">
         <v>1667</v>
       </c>
       <c r="C274" s="4" t="s">
@@ -20358,7 +20358,7 @@
       <c r="A275" s="4" t="s">
         <v>1685</v>
       </c>
-      <c r="B275" s="5" t="s">
+      <c r="B275" s="6" t="s">
         <v>1667</v>
       </c>
       <c r="C275" s="4" t="s">
@@ -20400,7 +20400,7 @@
       <c r="A276" s="4" t="s">
         <v>1691</v>
       </c>
-      <c r="B276" s="5" t="s">
+      <c r="B276" s="6" t="s">
         <v>1667</v>
       </c>
       <c r="C276" s="4" t="s">
@@ -20442,7 +20442,7 @@
       <c r="A277" s="4" t="s">
         <v>1697</v>
       </c>
-      <c r="B277" s="5" t="s">
+      <c r="B277" s="6" t="s">
         <v>1667</v>
       </c>
       <c r="C277" s="4" t="s">
@@ -20484,7 +20484,7 @@
       <c r="A278" s="4" t="s">
         <v>1703</v>
       </c>
-      <c r="B278" s="5" t="s">
+      <c r="B278" s="6" t="s">
         <v>1667</v>
       </c>
       <c r="C278" s="4" t="s">
@@ -20526,7 +20526,7 @@
       <c r="A279" s="4" t="s">
         <v>1709</v>
       </c>
-      <c r="B279" s="5" t="s">
+      <c r="B279" s="6" t="s">
         <v>1667</v>
       </c>
       <c r="C279" s="4" t="s">
@@ -20568,7 +20568,7 @@
       <c r="A280" s="4" t="s">
         <v>1715</v>
       </c>
-      <c r="B280" s="5" t="s">
+      <c r="B280" s="6" t="s">
         <v>1667</v>
       </c>
       <c r="C280" s="4" t="s">
@@ -20610,7 +20610,7 @@
       <c r="A281" s="4" t="s">
         <v>1721</v>
       </c>
-      <c r="B281" s="5" t="s">
+      <c r="B281" s="6" t="s">
         <v>1667</v>
       </c>
       <c r="C281" s="4" t="s">
@@ -20652,7 +20652,7 @@
       <c r="A282" s="4" t="s">
         <v>1727</v>
       </c>
-      <c r="B282" s="5" t="s">
+      <c r="B282" s="6" t="s">
         <v>1667</v>
       </c>
       <c r="C282" s="4" t="s">
@@ -20694,7 +20694,7 @@
       <c r="A283" s="4" t="s">
         <v>1733</v>
       </c>
-      <c r="B283" s="5" t="s">
+      <c r="B283" s="6" t="s">
         <v>1667</v>
       </c>
       <c r="C283" s="4" t="s">
@@ -20736,7 +20736,7 @@
       <c r="A284" s="4" t="s">
         <v>1739</v>
       </c>
-      <c r="B284" s="5" t="s">
+      <c r="B284" s="6" t="s">
         <v>1667</v>
       </c>
       <c r="C284" s="4" t="s">
@@ -20778,7 +20778,7 @@
       <c r="A285" s="4" t="s">
         <v>1745</v>
       </c>
-      <c r="B285" s="5" t="s">
+      <c r="B285" s="6" t="s">
         <v>1667</v>
       </c>
       <c r="C285" s="4" t="s">
@@ -20820,7 +20820,7 @@
       <c r="A286" s="4" t="s">
         <v>1751</v>
       </c>
-      <c r="B286" s="5" t="s">
+      <c r="B286" s="6" t="s">
         <v>1667</v>
       </c>
       <c r="C286" s="4" t="s">
@@ -20862,7 +20862,7 @@
       <c r="A287" s="4" t="s">
         <v>1757</v>
       </c>
-      <c r="B287" s="5" t="s">
+      <c r="B287" s="6" t="s">
         <v>1758</v>
       </c>
       <c r="C287" s="4" t="s">
@@ -20904,7 +20904,7 @@
       <c r="A288" s="4" t="s">
         <v>1764</v>
       </c>
-      <c r="B288" s="5" t="s">
+      <c r="B288" s="6" t="s">
         <v>1758</v>
       </c>
       <c r="C288" s="4" t="s">
@@ -20988,7 +20988,7 @@
       <c r="A290" s="4" t="s">
         <v>1776</v>
       </c>
-      <c r="B290" s="5" t="s">
+      <c r="B290" s="6" t="s">
         <v>1758</v>
       </c>
       <c r="C290" s="4" t="s">
@@ -21030,7 +21030,7 @@
       <c r="A291" s="4" t="s">
         <v>1782</v>
       </c>
-      <c r="B291" s="5" t="s">
+      <c r="B291" s="6" t="s">
         <v>1758</v>
       </c>
       <c r="C291" s="4" t="s">
@@ -21072,7 +21072,7 @@
       <c r="A292" s="4" t="s">
         <v>1788</v>
       </c>
-      <c r="B292" s="5" t="s">
+      <c r="B292" s="6" t="s">
         <v>1758</v>
       </c>
       <c r="C292" s="4" t="s">
@@ -21114,7 +21114,7 @@
       <c r="A293" s="4" t="s">
         <v>1794</v>
       </c>
-      <c r="B293" s="5" t="s">
+      <c r="B293" s="6" t="s">
         <v>1758</v>
       </c>
       <c r="C293" s="4" t="s">
@@ -21156,7 +21156,7 @@
       <c r="A294" s="4" t="s">
         <v>1800</v>
       </c>
-      <c r="B294" s="5" t="s">
+      <c r="B294" s="6" t="s">
         <v>1758</v>
       </c>
       <c r="C294" s="4" t="s">
@@ -21198,7 +21198,7 @@
       <c r="A295" s="4" t="s">
         <v>1806</v>
       </c>
-      <c r="B295" s="5" t="s">
+      <c r="B295" s="6" t="s">
         <v>1758</v>
       </c>
       <c r="C295" s="4" t="s">
@@ -21240,7 +21240,7 @@
       <c r="A296" s="4" t="s">
         <v>1812</v>
       </c>
-      <c r="B296" s="5" t="s">
+      <c r="B296" s="6" t="s">
         <v>1758</v>
       </c>
       <c r="C296" s="4" t="s">
@@ -21282,7 +21282,7 @@
       <c r="A297" s="4" t="s">
         <v>1818</v>
       </c>
-      <c r="B297" s="5" t="s">
+      <c r="B297" s="6" t="s">
         <v>1758</v>
       </c>
       <c r="C297" s="4" t="s">
@@ -21324,7 +21324,7 @@
       <c r="A298" s="4" t="s">
         <v>1824</v>
       </c>
-      <c r="B298" s="5" t="s">
+      <c r="B298" s="6" t="s">
         <v>1758</v>
       </c>
       <c r="C298" s="4" t="s">
@@ -21366,7 +21366,7 @@
       <c r="A299" s="4" t="s">
         <v>1830</v>
       </c>
-      <c r="B299" s="5" t="s">
+      <c r="B299" s="6" t="s">
         <v>1758</v>
       </c>
       <c r="C299" s="4" t="s">
@@ -21408,7 +21408,7 @@
       <c r="A300" s="4" t="s">
         <v>1836</v>
       </c>
-      <c r="B300" s="5" t="s">
+      <c r="B300" s="6" t="s">
         <v>1758</v>
       </c>
       <c r="C300" s="4" t="s">
@@ -21450,7 +21450,7 @@
       <c r="A301" s="4" t="s">
         <v>1842</v>
       </c>
-      <c r="B301" s="5" t="s">
+      <c r="B301" s="6" t="s">
         <v>1758</v>
       </c>
       <c r="C301" s="4" t="s">
@@ -21492,7 +21492,7 @@
       <c r="A302" s="4" t="s">
         <v>1848</v>
       </c>
-      <c r="B302" s="5" t="s">
+      <c r="B302" s="6" t="s">
         <v>1849</v>
       </c>
       <c r="C302" s="4" t="s">
@@ -21534,7 +21534,7 @@
       <c r="A303" s="4" t="s">
         <v>1855</v>
       </c>
-      <c r="B303" s="5" t="s">
+      <c r="B303" s="6" t="s">
         <v>1849</v>
       </c>
       <c r="C303" s="4" t="s">
@@ -21576,7 +21576,7 @@
       <c r="A304" s="4" t="s">
         <v>1861</v>
       </c>
-      <c r="B304" s="5" t="s">
+      <c r="B304" s="6" t="s">
         <v>1849</v>
       </c>
       <c r="C304" s="4" t="s">
@@ -21618,7 +21618,7 @@
       <c r="A305" s="4" t="s">
         <v>1867</v>
       </c>
-      <c r="B305" s="5" t="s">
+      <c r="B305" s="6" t="s">
         <v>1849</v>
       </c>
       <c r="C305" s="4" t="s">
@@ -21660,7 +21660,7 @@
       <c r="A306" s="4" t="s">
         <v>1873</v>
       </c>
-      <c r="B306" s="5" t="s">
+      <c r="B306" s="6" t="s">
         <v>1849</v>
       </c>
       <c r="C306" s="4" t="s">
@@ -21702,7 +21702,7 @@
       <c r="A307" s="4" t="s">
         <v>1879</v>
       </c>
-      <c r="B307" s="5" t="s">
+      <c r="B307" s="6" t="s">
         <v>1849</v>
       </c>
       <c r="C307" s="4" t="s">
@@ -21744,7 +21744,7 @@
       <c r="A308" s="4" t="s">
         <v>1885</v>
       </c>
-      <c r="B308" s="5" t="s">
+      <c r="B308" s="6" t="s">
         <v>1849</v>
       </c>
       <c r="C308" s="4" t="s">
@@ -21786,7 +21786,7 @@
       <c r="A309" s="4" t="s">
         <v>1891</v>
       </c>
-      <c r="B309" s="5" t="s">
+      <c r="B309" s="6" t="s">
         <v>1849</v>
       </c>
       <c r="C309" s="4" t="s">
@@ -21828,7 +21828,7 @@
       <c r="A310" s="4" t="s">
         <v>1897</v>
       </c>
-      <c r="B310" s="5" t="s">
+      <c r="B310" s="6" t="s">
         <v>1849</v>
       </c>
       <c r="C310" s="4" t="s">
@@ -21870,7 +21870,7 @@
       <c r="A311" s="4" t="s">
         <v>1903</v>
       </c>
-      <c r="B311" s="5" t="s">
+      <c r="B311" s="6" t="s">
         <v>1849</v>
       </c>
       <c r="C311" s="4" t="s">
@@ -21912,7 +21912,7 @@
       <c r="A312" s="4" t="s">
         <v>1909</v>
       </c>
-      <c r="B312" s="5" t="s">
+      <c r="B312" s="6" t="s">
         <v>1849</v>
       </c>
       <c r="C312" s="4" t="s">
@@ -21954,7 +21954,7 @@
       <c r="A313" s="4" t="s">
         <v>1915</v>
       </c>
-      <c r="B313" s="5" t="s">
+      <c r="B313" s="6" t="s">
         <v>1849</v>
       </c>
       <c r="C313" s="4" t="s">
@@ -21996,7 +21996,7 @@
       <c r="A314" s="4" t="s">
         <v>1921</v>
       </c>
-      <c r="B314" s="5" t="s">
+      <c r="B314" s="6" t="s">
         <v>1849</v>
       </c>
       <c r="C314" s="4" t="s">
@@ -22038,7 +22038,7 @@
       <c r="A315" s="4" t="s">
         <v>1927</v>
       </c>
-      <c r="B315" s="5" t="s">
+      <c r="B315" s="6" t="s">
         <v>1849</v>
       </c>
       <c r="C315" s="4" t="s">
@@ -22080,7 +22080,7 @@
       <c r="A316" s="4" t="s">
         <v>1933</v>
       </c>
-      <c r="B316" s="5" t="s">
+      <c r="B316" s="6" t="s">
         <v>1849</v>
       </c>
       <c r="C316" s="4" t="s">
@@ -22122,7 +22122,7 @@
       <c r="A317" s="4" t="s">
         <v>1939</v>
       </c>
-      <c r="B317" s="5" t="s">
+      <c r="B317" s="6" t="s">
         <v>1940</v>
       </c>
       <c r="C317" s="4" t="s">
@@ -22164,7 +22164,7 @@
       <c r="A318" s="4" t="s">
         <v>1946</v>
       </c>
-      <c r="B318" s="5" t="s">
+      <c r="B318" s="6" t="s">
         <v>1940</v>
       </c>
       <c r="C318" s="4" t="s">
@@ -22206,7 +22206,7 @@
       <c r="A319" s="4" t="s">
         <v>1952</v>
       </c>
-      <c r="B319" s="5" t="s">
+      <c r="B319" s="6" t="s">
         <v>1940</v>
       </c>
       <c r="C319" s="4" t="s">
@@ -22248,7 +22248,7 @@
       <c r="A320" s="4" t="s">
         <v>1958</v>
       </c>
-      <c r="B320" s="5" t="s">
+      <c r="B320" s="6" t="s">
         <v>1940</v>
       </c>
       <c r="C320" s="4" t="s">
@@ -22290,7 +22290,7 @@
       <c r="A321" s="4" t="s">
         <v>1964</v>
       </c>
-      <c r="B321" s="5" t="s">
+      <c r="B321" s="6" t="s">
         <v>1940</v>
       </c>
       <c r="C321" s="4" t="s">
@@ -22332,7 +22332,7 @@
       <c r="A322" s="4" t="s">
         <v>1970</v>
       </c>
-      <c r="B322" s="5" t="s">
+      <c r="B322" s="6" t="s">
         <v>1940</v>
       </c>
       <c r="C322" s="4" t="s">
@@ -22374,7 +22374,7 @@
       <c r="A323" s="4" t="s">
         <v>1976</v>
       </c>
-      <c r="B323" s="5" t="s">
+      <c r="B323" s="6" t="s">
         <v>1940</v>
       </c>
       <c r="C323" s="4" t="s">
@@ -22416,7 +22416,7 @@
       <c r="A324" s="4" t="s">
         <v>1982</v>
       </c>
-      <c r="B324" s="5" t="s">
+      <c r="B324" s="6" t="s">
         <v>1940</v>
       </c>
       <c r="C324" s="4" t="s">
@@ -22458,7 +22458,7 @@
       <c r="A325" s="4" t="s">
         <v>1988</v>
       </c>
-      <c r="B325" s="5" t="s">
+      <c r="B325" s="6" t="s">
         <v>1940</v>
       </c>
       <c r="C325" s="4" t="s">
@@ -22500,7 +22500,7 @@
       <c r="A326" s="4" t="s">
         <v>1994</v>
       </c>
-      <c r="B326" s="5" t="s">
+      <c r="B326" s="6" t="s">
         <v>1940</v>
       </c>
       <c r="C326" s="4" t="s">
@@ -22542,7 +22542,7 @@
       <c r="A327" s="4" t="s">
         <v>2000</v>
       </c>
-      <c r="B327" s="5" t="s">
+      <c r="B327" s="6" t="s">
         <v>1940</v>
       </c>
       <c r="C327" s="4" t="s">
@@ -22584,7 +22584,7 @@
       <c r="A328" s="4" t="s">
         <v>2006</v>
       </c>
-      <c r="B328" s="5" t="s">
+      <c r="B328" s="6" t="s">
         <v>1940</v>
       </c>
       <c r="C328" s="4" t="s">
@@ -22626,7 +22626,7 @@
       <c r="A329" s="4" t="s">
         <v>2012</v>
       </c>
-      <c r="B329" s="5" t="s">
+      <c r="B329" s="6" t="s">
         <v>1940</v>
       </c>
       <c r="C329" s="4" t="s">
@@ -22668,7 +22668,7 @@
       <c r="A330" s="4" t="s">
         <v>2018</v>
       </c>
-      <c r="B330" s="5" t="s">
+      <c r="B330" s="6" t="s">
         <v>1940</v>
       </c>
       <c r="C330" s="4" t="s">
@@ -22710,7 +22710,7 @@
       <c r="A331" s="4" t="s">
         <v>2024</v>
       </c>
-      <c r="B331" s="5" t="s">
+      <c r="B331" s="6" t="s">
         <v>2025</v>
       </c>
       <c r="C331" s="4" t="s">
@@ -22752,7 +22752,7 @@
       <c r="A332" s="4" t="s">
         <v>2031</v>
       </c>
-      <c r="B332" s="5" t="s">
+      <c r="B332" s="6" t="s">
         <v>2025</v>
       </c>
       <c r="C332" s="4" t="s">
@@ -22794,7 +22794,7 @@
       <c r="A333" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="B333" s="5" t="s">
+      <c r="B333" s="6" t="s">
         <v>2025</v>
       </c>
       <c r="C333" s="4" t="s">
@@ -22836,7 +22836,7 @@
       <c r="A334" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="B334" s="5" t="s">
+      <c r="B334" s="6" t="s">
         <v>2025</v>
       </c>
       <c r="C334" s="4" t="s">
@@ -22878,7 +22878,7 @@
       <c r="A335" s="4" t="s">
         <v>2049</v>
       </c>
-      <c r="B335" s="5" t="s">
+      <c r="B335" s="6" t="s">
         <v>2025</v>
       </c>
       <c r="C335" s="4" t="s">
@@ -22920,7 +22920,7 @@
       <c r="A336" s="4" t="s">
         <v>2055</v>
       </c>
-      <c r="B336" s="5" t="s">
+      <c r="B336" s="6" t="s">
         <v>2025</v>
       </c>
       <c r="C336" s="4" t="s">
@@ -22962,7 +22962,7 @@
       <c r="A337" s="4" t="s">
         <v>2061</v>
       </c>
-      <c r="B337" s="5" t="s">
+      <c r="B337" s="6" t="s">
         <v>2025</v>
       </c>
       <c r="C337" s="4" t="s">
@@ -23004,7 +23004,7 @@
       <c r="A338" s="4" t="s">
         <v>2067</v>
       </c>
-      <c r="B338" s="5" t="s">
+      <c r="B338" s="6" t="s">
         <v>2025</v>
       </c>
       <c r="C338" s="4" t="s">
@@ -23046,7 +23046,7 @@
       <c r="A339" s="4" t="s">
         <v>2073</v>
       </c>
-      <c r="B339" s="5" t="s">
+      <c r="B339" s="6" t="s">
         <v>2025</v>
       </c>
       <c r="C339" s="4" t="s">
@@ -23088,7 +23088,7 @@
       <c r="A340" s="4" t="s">
         <v>2079</v>
       </c>
-      <c r="B340" s="5" t="s">
+      <c r="B340" s="6" t="s">
         <v>2025</v>
       </c>
       <c r="C340" s="4" t="s">
@@ -23130,7 +23130,7 @@
       <c r="A341" s="4" t="s">
         <v>2085</v>
       </c>
-      <c r="B341" s="5" t="s">
+      <c r="B341" s="6" t="s">
         <v>2025</v>
       </c>
       <c r="C341" s="4" t="s">
@@ -23172,7 +23172,7 @@
       <c r="A342" s="4" t="s">
         <v>2091</v>
       </c>
-      <c r="B342" s="5" t="s">
+      <c r="B342" s="6" t="s">
         <v>2025</v>
       </c>
       <c r="C342" s="4" t="s">
@@ -23214,7 +23214,7 @@
       <c r="A343" s="4" t="s">
         <v>2097</v>
       </c>
-      <c r="B343" s="5" t="s">
+      <c r="B343" s="6" t="s">
         <v>2025</v>
       </c>
       <c r="C343" s="4" t="s">
@@ -23256,7 +23256,7 @@
       <c r="A344" s="4" t="s">
         <v>2103</v>
       </c>
-      <c r="B344" s="5" t="s">
+      <c r="B344" s="6" t="s">
         <v>2025</v>
       </c>
       <c r="C344" s="4" t="s">
@@ -23298,7 +23298,7 @@
       <c r="A345" s="4" t="s">
         <v>2109</v>
       </c>
-      <c r="B345" s="5" t="s">
+      <c r="B345" s="6" t="s">
         <v>2025</v>
       </c>
       <c r="C345" s="4" t="s">
@@ -23340,7 +23340,7 @@
       <c r="A346" s="4" t="s">
         <v>2115</v>
       </c>
-      <c r="B346" s="5" t="s">
+      <c r="B346" s="6" t="s">
         <v>2116</v>
       </c>
       <c r="C346" s="4" t="s">
@@ -23382,7 +23382,7 @@
       <c r="A347" s="4" t="s">
         <v>2122</v>
       </c>
-      <c r="B347" s="5" t="s">
+      <c r="B347" s="6" t="s">
         <v>2116</v>
       </c>
       <c r="C347" s="4" t="s">
@@ -23424,7 +23424,7 @@
       <c r="A348" s="4" t="s">
         <v>2128</v>
       </c>
-      <c r="B348" s="5" t="s">
+      <c r="B348" s="6" t="s">
         <v>2116</v>
       </c>
       <c r="C348" s="4" t="s">
@@ -23466,7 +23466,7 @@
       <c r="A349" s="4" t="s">
         <v>2134</v>
       </c>
-      <c r="B349" s="5" t="s">
+      <c r="B349" s="6" t="s">
         <v>2116</v>
       </c>
       <c r="C349" s="4" t="s">
@@ -23508,7 +23508,7 @@
       <c r="A350" s="4" t="s">
         <v>2140</v>
       </c>
-      <c r="B350" s="5" t="s">
+      <c r="B350" s="6" t="s">
         <v>2116</v>
       </c>
       <c r="C350" s="4" t="s">
@@ -23550,7 +23550,7 @@
       <c r="A351" s="4" t="s">
         <v>2146</v>
       </c>
-      <c r="B351" s="5" t="s">
+      <c r="B351" s="6" t="s">
         <v>2116</v>
       </c>
       <c r="C351" s="4" t="s">
@@ -23592,7 +23592,7 @@
       <c r="A352" s="4" t="s">
         <v>2152</v>
       </c>
-      <c r="B352" s="5" t="s">
+      <c r="B352" s="6" t="s">
         <v>2116</v>
       </c>
       <c r="C352" s="4" t="s">
@@ -23634,7 +23634,7 @@
       <c r="A353" s="4" t="s">
         <v>2158</v>
       </c>
-      <c r="B353" s="5" t="s">
+      <c r="B353" s="6" t="s">
         <v>2116</v>
       </c>
       <c r="C353" s="4" t="s">
@@ -23676,7 +23676,7 @@
       <c r="A354" s="4" t="s">
         <v>2164</v>
       </c>
-      <c r="B354" s="5" t="s">
+      <c r="B354" s="6" t="s">
         <v>2116</v>
       </c>
       <c r="C354" s="4" t="s">
@@ -23718,7 +23718,7 @@
       <c r="A355" s="4" t="s">
         <v>2170</v>
       </c>
-      <c r="B355" s="5" t="s">
+      <c r="B355" s="6" t="s">
         <v>2116</v>
       </c>
       <c r="C355" s="4" t="s">
@@ -23760,7 +23760,7 @@
       <c r="A356" s="4" t="s">
         <v>2176</v>
       </c>
-      <c r="B356" s="5" t="s">
+      <c r="B356" s="6" t="s">
         <v>2116</v>
       </c>
       <c r="C356" s="4" t="s">
@@ -23802,7 +23802,7 @@
       <c r="A357" s="4" t="s">
         <v>2182</v>
       </c>
-      <c r="B357" s="5" t="s">
+      <c r="B357" s="6" t="s">
         <v>2116</v>
       </c>
       <c r="C357" s="4" t="s">
@@ -23844,7 +23844,7 @@
       <c r="A358" s="4" t="s">
         <v>2188</v>
       </c>
-      <c r="B358" s="5" t="s">
+      <c r="B358" s="6" t="s">
         <v>2116</v>
       </c>
       <c r="C358" s="4" t="s">
@@ -23886,7 +23886,7 @@
       <c r="A359" s="4" t="s">
         <v>2194</v>
       </c>
-      <c r="B359" s="5" t="s">
+      <c r="B359" s="6" t="s">
         <v>2116</v>
       </c>
       <c r="C359" s="4" t="s">
@@ -23928,7 +23928,7 @@
       <c r="A360" s="4" t="s">
         <v>2200</v>
       </c>
-      <c r="B360" s="5" t="s">
+      <c r="B360" s="6" t="s">
         <v>2116</v>
       </c>
       <c r="C360" s="4" t="s">
@@ -23970,7 +23970,7 @@
       <c r="A361" s="4" t="s">
         <v>2206</v>
       </c>
-      <c r="B361" s="5" t="s">
+      <c r="B361" s="6" t="s">
         <v>2207</v>
       </c>
       <c r="C361" s="4" t="s">
@@ -24012,7 +24012,7 @@
       <c r="A362" s="4" t="s">
         <v>2213</v>
       </c>
-      <c r="B362" s="5" t="s">
+      <c r="B362" s="6" t="s">
         <v>2207</v>
       </c>
       <c r="C362" s="4" t="s">
@@ -24054,7 +24054,7 @@
       <c r="A363" s="4" t="s">
         <v>2219</v>
       </c>
-      <c r="B363" s="5" t="s">
+      <c r="B363" s="6" t="s">
         <v>2207</v>
       </c>
       <c r="C363" s="4" t="s">
@@ -24096,7 +24096,7 @@
       <c r="A364" s="4" t="s">
         <v>2225</v>
       </c>
-      <c r="B364" s="5" t="s">
+      <c r="B364" s="6" t="s">
         <v>2207</v>
       </c>
       <c r="C364" s="4" t="s">
@@ -24138,7 +24138,7 @@
       <c r="A365" s="4" t="s">
         <v>2231</v>
       </c>
-      <c r="B365" s="5" t="s">
+      <c r="B365" s="6" t="s">
         <v>2207</v>
       </c>
       <c r="C365" s="4" t="s">
@@ -24180,7 +24180,7 @@
       <c r="A366" s="4" t="s">
         <v>2237</v>
       </c>
-      <c r="B366" s="5" t="s">
+      <c r="B366" s="6" t="s">
         <v>2207</v>
       </c>
       <c r="C366" s="4" t="s">
@@ -24222,7 +24222,7 @@
       <c r="A367" s="4" t="s">
         <v>2243</v>
       </c>
-      <c r="B367" s="5" t="s">
+      <c r="B367" s="6" t="s">
         <v>2207</v>
       </c>
       <c r="C367" s="4" t="s">
@@ -24264,7 +24264,7 @@
       <c r="A368" s="4" t="s">
         <v>2249</v>
       </c>
-      <c r="B368" s="5" t="s">
+      <c r="B368" s="6" t="s">
         <v>2207</v>
       </c>
       <c r="C368" s="4" t="s">
@@ -24306,7 +24306,7 @@
       <c r="A369" s="4" t="s">
         <v>2255</v>
       </c>
-      <c r="B369" s="5" t="s">
+      <c r="B369" s="6" t="s">
         <v>2207</v>
       </c>
       <c r="C369" s="4" t="s">
@@ -24348,7 +24348,7 @@
       <c r="A370" s="4" t="s">
         <v>2261</v>
       </c>
-      <c r="B370" s="5" t="s">
+      <c r="B370" s="6" t="s">
         <v>2207</v>
       </c>
       <c r="C370" s="4" t="s">
@@ -24390,7 +24390,7 @@
       <c r="A371" s="4" t="s">
         <v>2267</v>
       </c>
-      <c r="B371" s="5" t="s">
+      <c r="B371" s="6" t="s">
         <v>2207</v>
       </c>
       <c r="C371" s="4" t="s">
@@ -24432,7 +24432,7 @@
       <c r="A372" s="4" t="s">
         <v>2273</v>
       </c>
-      <c r="B372" s="5" t="s">
+      <c r="B372" s="6" t="s">
         <v>2207</v>
       </c>
       <c r="C372" s="4" t="s">
@@ -24474,7 +24474,7 @@
       <c r="A373" s="4" t="s">
         <v>2279</v>
       </c>
-      <c r="B373" s="5" t="s">
+      <c r="B373" s="6" t="s">
         <v>2207</v>
       </c>
       <c r="C373" s="4" t="s">
@@ -24516,7 +24516,7 @@
       <c r="A374" s="4" t="s">
         <v>2285</v>
       </c>
-      <c r="B374" s="5" t="s">
+      <c r="B374" s="6" t="s">
         <v>2207</v>
       </c>
       <c r="C374" s="4" t="s">
@@ -24558,7 +24558,7 @@
       <c r="A375" s="4" t="s">
         <v>2291</v>
       </c>
-      <c r="B375" s="5" t="s">
+      <c r="B375" s="6" t="s">
         <v>2207</v>
       </c>
       <c r="C375" s="4" t="s">
@@ -24600,7 +24600,7 @@
       <c r="A376" s="4" t="s">
         <v>2297</v>
       </c>
-      <c r="B376" s="5" t="s">
+      <c r="B376" s="6" t="s">
         <v>2298</v>
       </c>
       <c r="C376" s="4" t="s">
@@ -24642,7 +24642,7 @@
       <c r="A377" s="4" t="s">
         <v>2304</v>
       </c>
-      <c r="B377" s="5" t="s">
+      <c r="B377" s="6" t="s">
         <v>2298</v>
       </c>
       <c r="C377" s="4" t="s">
@@ -24684,7 +24684,7 @@
       <c r="A378" s="4" t="s">
         <v>2310</v>
       </c>
-      <c r="B378" s="5" t="s">
+      <c r="B378" s="6" t="s">
         <v>2298</v>
       </c>
       <c r="C378" s="4" t="s">
@@ -24726,7 +24726,7 @@
       <c r="A379" s="4" t="s">
         <v>2316</v>
       </c>
-      <c r="B379" s="5" t="s">
+      <c r="B379" s="6" t="s">
         <v>2298</v>
       </c>
       <c r="C379" s="4" t="s">
@@ -24768,7 +24768,7 @@
       <c r="A380" s="4" t="s">
         <v>2322</v>
       </c>
-      <c r="B380" s="5" t="s">
+      <c r="B380" s="6" t="s">
         <v>2298</v>
       </c>
       <c r="C380" s="4" t="s">
@@ -24810,7 +24810,7 @@
       <c r="A381" s="4" t="s">
         <v>2328</v>
       </c>
-      <c r="B381" s="5" t="s">
+      <c r="B381" s="6" t="s">
         <v>2298</v>
       </c>
       <c r="C381" s="4" t="s">
@@ -24852,7 +24852,7 @@
       <c r="A382" s="4" t="s">
         <v>2334</v>
       </c>
-      <c r="B382" s="5" t="s">
+      <c r="B382" s="6" t="s">
         <v>2298</v>
       </c>
       <c r="C382" s="4" t="s">
@@ -24894,7 +24894,7 @@
       <c r="A383" s="4" t="s">
         <v>2340</v>
       </c>
-      <c r="B383" s="5" t="s">
+      <c r="B383" s="6" t="s">
         <v>2298</v>
       </c>
       <c r="C383" s="4" t="s">
@@ -24936,7 +24936,7 @@
       <c r="A384" s="4" t="s">
         <v>2346</v>
       </c>
-      <c r="B384" s="5" t="s">
+      <c r="B384" s="6" t="s">
         <v>2298</v>
       </c>
       <c r="C384" s="4" t="s">
@@ -24978,7 +24978,7 @@
       <c r="A385" s="4" t="s">
         <v>2352</v>
       </c>
-      <c r="B385" s="5" t="s">
+      <c r="B385" s="6" t="s">
         <v>2298</v>
       </c>
       <c r="C385" s="4" t="s">
@@ -25020,7 +25020,7 @@
       <c r="A386" s="4" t="s">
         <v>2358</v>
       </c>
-      <c r="B386" s="5" t="s">
+      <c r="B386" s="6" t="s">
         <v>2298</v>
       </c>
       <c r="C386" s="4" t="s">
@@ -25062,7 +25062,7 @@
       <c r="A387" s="4" t="s">
         <v>2364</v>
       </c>
-      <c r="B387" s="5" t="s">
+      <c r="B387" s="6" t="s">
         <v>2298</v>
       </c>
       <c r="C387" s="4" t="s">
@@ -25104,7 +25104,7 @@
       <c r="A388" s="4" t="s">
         <v>2370</v>
       </c>
-      <c r="B388" s="5" t="s">
+      <c r="B388" s="6" t="s">
         <v>2298</v>
       </c>
       <c r="C388" s="4" t="s">
@@ -25146,7 +25146,7 @@
       <c r="A389" s="4" t="s">
         <v>2376</v>
       </c>
-      <c r="B389" s="5" t="s">
+      <c r="B389" s="6" t="s">
         <v>2298</v>
       </c>
       <c r="C389" s="4" t="s">
@@ -25188,7 +25188,7 @@
       <c r="A390" s="4" t="s">
         <v>2382</v>
       </c>
-      <c r="B390" s="5" t="s">
+      <c r="B390" s="6" t="s">
         <v>2298</v>
       </c>
       <c r="C390" s="4" t="s">
@@ -25230,7 +25230,7 @@
       <c r="A391" s="4" t="s">
         <v>2388</v>
       </c>
-      <c r="B391" s="5" t="s">
+      <c r="B391" s="6" t="s">
         <v>2389</v>
       </c>
       <c r="C391" s="4" t="s">
@@ -25272,7 +25272,7 @@
       <c r="A392" s="4" t="s">
         <v>2395</v>
       </c>
-      <c r="B392" s="5" t="s">
+      <c r="B392" s="6" t="s">
         <v>2389</v>
       </c>
       <c r="C392" s="4" t="s">
@@ -25314,7 +25314,7 @@
       <c r="A393" s="4" t="s">
         <v>2401</v>
       </c>
-      <c r="B393" s="5" t="s">
+      <c r="B393" s="6" t="s">
         <v>2389</v>
       </c>
       <c r="C393" s="4" t="s">
@@ -25356,7 +25356,7 @@
       <c r="A394" s="4" t="s">
         <v>2407</v>
       </c>
-      <c r="B394" s="5" t="s">
+      <c r="B394" s="6" t="s">
         <v>2389</v>
       </c>
       <c r="C394" s="4" t="s">
@@ -25398,7 +25398,7 @@
       <c r="A395" s="4" t="s">
         <v>2413</v>
       </c>
-      <c r="B395" s="5" t="s">
+      <c r="B395" s="6" t="s">
         <v>2389</v>
       </c>
       <c r="C395" s="4" t="s">
@@ -25440,7 +25440,7 @@
       <c r="A396" s="4" t="s">
         <v>2419</v>
       </c>
-      <c r="B396" s="5" t="s">
+      <c r="B396" s="6" t="s">
         <v>2389</v>
       </c>
       <c r="C396" s="4" t="s">
@@ -25482,7 +25482,7 @@
       <c r="A397" s="4" t="s">
         <v>2425</v>
       </c>
-      <c r="B397" s="5" t="s">
+      <c r="B397" s="6" t="s">
         <v>2389</v>
       </c>
       <c r="C397" s="4" t="s">
@@ -25524,7 +25524,7 @@
       <c r="A398" s="4" t="s">
         <v>2431</v>
       </c>
-      <c r="B398" s="5" t="s">
+      <c r="B398" s="6" t="s">
         <v>2389</v>
       </c>
       <c r="C398" s="4" t="s">
@@ -25566,7 +25566,7 @@
       <c r="A399" s="4" t="s">
         <v>2437</v>
       </c>
-      <c r="B399" s="5" t="s">
+      <c r="B399" s="6" t="s">
         <v>2389</v>
       </c>
       <c r="C399" s="4" t="s">
@@ -25608,7 +25608,7 @@
       <c r="A400" s="4" t="s">
         <v>2443</v>
       </c>
-      <c r="B400" s="5" t="s">
+      <c r="B400" s="6" t="s">
         <v>2389</v>
       </c>
       <c r="C400" s="4" t="s">
@@ -25650,7 +25650,7 @@
       <c r="A401" s="4" t="s">
         <v>2449</v>
       </c>
-      <c r="B401" s="5" t="s">
+      <c r="B401" s="6" t="s">
         <v>2389</v>
       </c>
       <c r="C401" s="4" t="s">
@@ -25692,7 +25692,7 @@
       <c r="A402" s="4" t="s">
         <v>2455</v>
       </c>
-      <c r="B402" s="5" t="s">
+      <c r="B402" s="6" t="s">
         <v>2389</v>
       </c>
       <c r="C402" s="4" t="s">
@@ -25734,7 +25734,7 @@
       <c r="A403" s="4" t="s">
         <v>2461</v>
       </c>
-      <c r="B403" s="5" t="s">
+      <c r="B403" s="6" t="s">
         <v>2389</v>
       </c>
       <c r="C403" s="4" t="s">
@@ -25776,7 +25776,7 @@
       <c r="A404" s="4" t="s">
         <v>2467</v>
       </c>
-      <c r="B404" s="5" t="s">
+      <c r="B404" s="6" t="s">
         <v>2389</v>
       </c>
       <c r="C404" s="4" t="s">
@@ -25818,7 +25818,7 @@
       <c r="A405" s="4" t="s">
         <v>2473</v>
       </c>
-      <c r="B405" s="5" t="s">
+      <c r="B405" s="6" t="s">
         <v>2389</v>
       </c>
       <c r="C405" s="4" t="s">
@@ -25902,7 +25902,7 @@
       <c r="A407" s="4" t="s">
         <v>2486</v>
       </c>
-      <c r="B407" s="5" t="s">
+      <c r="B407" s="6" t="s">
         <v>2480</v>
       </c>
       <c r="C407" s="4" t="s">
@@ -25944,7 +25944,7 @@
       <c r="A408" s="4" t="s">
         <v>2492</v>
       </c>
-      <c r="B408" s="5" t="s">
+      <c r="B408" s="6" t="s">
         <v>2480</v>
       </c>
       <c r="C408" s="4" t="s">
@@ -25986,7 +25986,7 @@
       <c r="A409" s="4" t="s">
         <v>2498</v>
       </c>
-      <c r="B409" s="5" t="s">
+      <c r="B409" s="6" t="s">
         <v>2480</v>
       </c>
       <c r="C409" s="4" t="s">
@@ -26028,7 +26028,7 @@
       <c r="A410" s="4" t="s">
         <v>2504</v>
       </c>
-      <c r="B410" s="5" t="s">
+      <c r="B410" s="6" t="s">
         <v>2480</v>
       </c>
       <c r="C410" s="4" t="s">
@@ -26070,7 +26070,7 @@
       <c r="A411" s="4" t="s">
         <v>2510</v>
       </c>
-      <c r="B411" s="5" t="s">
+      <c r="B411" s="6" t="s">
         <v>2480</v>
       </c>
       <c r="C411" s="4" t="s">
@@ -26112,7 +26112,7 @@
       <c r="A412" s="4" t="s">
         <v>2516</v>
       </c>
-      <c r="B412" s="5" t="s">
+      <c r="B412" s="6" t="s">
         <v>2480</v>
       </c>
       <c r="C412" s="4" t="s">
@@ -26154,7 +26154,7 @@
       <c r="A413" s="4" t="s">
         <v>2522</v>
       </c>
-      <c r="B413" s="5" t="s">
+      <c r="B413" s="6" t="s">
         <v>2480</v>
       </c>
       <c r="C413" s="4" t="s">
@@ -26196,7 +26196,7 @@
       <c r="A414" s="4" t="s">
         <v>2528</v>
       </c>
-      <c r="B414" s="5" t="s">
+      <c r="B414" s="6" t="s">
         <v>2480</v>
       </c>
       <c r="C414" s="4" t="s">
@@ -26238,7 +26238,7 @@
       <c r="A415" s="4" t="s">
         <v>2534</v>
       </c>
-      <c r="B415" s="5" t="s">
+      <c r="B415" s="6" t="s">
         <v>2480</v>
       </c>
       <c r="C415" s="4" t="s">
@@ -26280,7 +26280,7 @@
       <c r="A416" s="4" t="s">
         <v>2540</v>
       </c>
-      <c r="B416" s="5" t="s">
+      <c r="B416" s="6" t="s">
         <v>2480</v>
       </c>
       <c r="C416" s="4" t="s">
@@ -26322,7 +26322,7 @@
       <c r="A417" s="4" t="s">
         <v>2546</v>
       </c>
-      <c r="B417" s="5" t="s">
+      <c r="B417" s="6" t="s">
         <v>2480</v>
       </c>
       <c r="C417" s="4" t="s">
@@ -26364,7 +26364,7 @@
       <c r="A418" s="4" t="s">
         <v>2552</v>
       </c>
-      <c r="B418" s="5" t="s">
+      <c r="B418" s="6" t="s">
         <v>2480</v>
       </c>
       <c r="C418" s="4" t="s">
@@ -26406,7 +26406,7 @@
       <c r="A419" s="4" t="s">
         <v>2558</v>
       </c>
-      <c r="B419" s="5" t="s">
+      <c r="B419" s="6" t="s">
         <v>2480</v>
       </c>
       <c r="C419" s="4" t="s">
@@ -26448,7 +26448,7 @@
       <c r="A420" s="4" t="s">
         <v>2564</v>
       </c>
-      <c r="B420" s="5" t="s">
+      <c r="B420" s="6" t="s">
         <v>2480</v>
       </c>
       <c r="C420" s="4" t="s">
@@ -26490,7 +26490,7 @@
       <c r="A421" s="4" t="s">
         <v>2570</v>
       </c>
-      <c r="B421" s="5" t="s">
+      <c r="B421" s="6" t="s">
         <v>2571</v>
       </c>
       <c r="C421" s="4" t="s">
@@ -26532,7 +26532,7 @@
       <c r="A422" s="4" t="s">
         <v>2577</v>
       </c>
-      <c r="B422" s="5" t="s">
+      <c r="B422" s="6" t="s">
         <v>2571</v>
       </c>
       <c r="C422" s="4" t="s">
@@ -26574,7 +26574,7 @@
       <c r="A423" s="4" t="s">
         <v>2583</v>
       </c>
-      <c r="B423" s="5" t="s">
+      <c r="B423" s="6" t="s">
         <v>2571</v>
       </c>
       <c r="C423" s="4" t="s">
@@ -26616,7 +26616,7 @@
       <c r="A424" s="4" t="s">
         <v>2589</v>
       </c>
-      <c r="B424" s="5" t="s">
+      <c r="B424" s="6" t="s">
         <v>2571</v>
       </c>
       <c r="C424" s="4" t="s">
@@ -26658,7 +26658,7 @@
       <c r="A425" s="4" t="s">
         <v>2595</v>
       </c>
-      <c r="B425" s="5" t="s">
+      <c r="B425" s="6" t="s">
         <v>2571</v>
       </c>
       <c r="C425" s="4" t="s">
@@ -26700,7 +26700,7 @@
       <c r="A426" s="4" t="s">
         <v>2601</v>
       </c>
-      <c r="B426" s="5" t="s">
+      <c r="B426" s="6" t="s">
         <v>2571</v>
       </c>
       <c r="C426" s="4" t="s">
@@ -26742,7 +26742,7 @@
       <c r="A427" s="4" t="s">
         <v>2607</v>
       </c>
-      <c r="B427" s="5" t="s">
+      <c r="B427" s="6" t="s">
         <v>2571</v>
       </c>
       <c r="C427" s="4" t="s">
@@ -26784,7 +26784,7 @@
       <c r="A428" s="4" t="s">
         <v>2613</v>
       </c>
-      <c r="B428" s="5" t="s">
+      <c r="B428" s="6" t="s">
         <v>2571</v>
       </c>
       <c r="C428" s="4" t="s">
@@ -26826,7 +26826,7 @@
       <c r="A429" s="4" t="s">
         <v>2619</v>
       </c>
-      <c r="B429" s="5" t="s">
+      <c r="B429" s="6" t="s">
         <v>2571</v>
       </c>
       <c r="C429" s="4" t="s">
@@ -26868,7 +26868,7 @@
       <c r="A430" s="4" t="s">
         <v>2625</v>
       </c>
-      <c r="B430" s="5" t="s">
+      <c r="B430" s="6" t="s">
         <v>2571</v>
       </c>
       <c r="C430" s="4" t="s">
@@ -26910,7 +26910,7 @@
       <c r="A431" s="4" t="s">
         <v>2631</v>
       </c>
-      <c r="B431" s="5" t="s">
+      <c r="B431" s="6" t="s">
         <v>2571</v>
       </c>
       <c r="C431" s="4" t="s">
@@ -26952,7 +26952,7 @@
       <c r="A432" s="4" t="s">
         <v>2637</v>
       </c>
-      <c r="B432" s="5" t="s">
+      <c r="B432" s="6" t="s">
         <v>2571</v>
       </c>
       <c r="C432" s="4" t="s">
@@ -26994,7 +26994,7 @@
       <c r="A433" s="4" t="s">
         <v>2643</v>
       </c>
-      <c r="B433" s="5" t="s">
+      <c r="B433" s="6" t="s">
         <v>2571</v>
       </c>
       <c r="C433" s="4" t="s">
@@ -27036,7 +27036,7 @@
       <c r="A434" s="4" t="s">
         <v>2649</v>
       </c>
-      <c r="B434" s="5" t="s">
+      <c r="B434" s="6" t="s">
         <v>2571</v>
       </c>
       <c r="C434" s="4" t="s">
@@ -27078,7 +27078,7 @@
       <c r="A435" s="4" t="s">
         <v>2655</v>
       </c>
-      <c r="B435" s="5" t="s">
+      <c r="B435" s="6" t="s">
         <v>2571</v>
       </c>
       <c r="C435" s="4" t="s">
@@ -27120,7 +27120,7 @@
       <c r="A436" s="4" t="s">
         <v>2661</v>
       </c>
-      <c r="B436" s="5" t="s">
+      <c r="B436" s="6" t="s">
         <v>2662</v>
       </c>
       <c r="C436" s="4" t="s">
@@ -27162,7 +27162,7 @@
       <c r="A437" s="4" t="s">
         <v>2668</v>
       </c>
-      <c r="B437" s="5" t="s">
+      <c r="B437" s="6" t="s">
         <v>2662</v>
       </c>
       <c r="C437" s="4" t="s">
@@ -27204,7 +27204,7 @@
       <c r="A438" s="4" t="s">
         <v>2674</v>
       </c>
-      <c r="B438" s="5" t="s">
+      <c r="B438" s="6" t="s">
         <v>2662</v>
       </c>
       <c r="C438" s="4" t="s">
@@ -27246,7 +27246,7 @@
       <c r="A439" s="4" t="s">
         <v>2680</v>
       </c>
-      <c r="B439" s="5" t="s">
+      <c r="B439" s="6" t="s">
         <v>2662</v>
       </c>
       <c r="C439" s="4" t="s">
@@ -27288,7 +27288,7 @@
       <c r="A440" s="4" t="s">
         <v>2686</v>
       </c>
-      <c r="B440" s="5" t="s">
+      <c r="B440" s="6" t="s">
         <v>2662</v>
       </c>
       <c r="C440" s="4" t="s">
@@ -27330,7 +27330,7 @@
       <c r="A441" s="4" t="s">
         <v>2692</v>
       </c>
-      <c r="B441" s="5" t="s">
+      <c r="B441" s="6" t="s">
         <v>2662</v>
       </c>
       <c r="C441" s="4" t="s">
@@ -27372,7 +27372,7 @@
       <c r="A442" s="4" t="s">
         <v>2698</v>
       </c>
-      <c r="B442" s="5" t="s">
+      <c r="B442" s="6" t="s">
         <v>2662</v>
       </c>
       <c r="C442" s="4" t="s">
@@ -27414,7 +27414,7 @@
       <c r="A443" s="4" t="s">
         <v>2704</v>
       </c>
-      <c r="B443" s="5" t="s">
+      <c r="B443" s="6" t="s">
         <v>2662</v>
       </c>
       <c r="C443" s="4" t="s">
@@ -27456,7 +27456,7 @@
       <c r="A444" s="4" t="s">
         <v>2710</v>
       </c>
-      <c r="B444" s="5" t="s">
+      <c r="B444" s="6" t="s">
         <v>2662</v>
       </c>
       <c r="C444" s="4" t="s">
@@ -27498,7 +27498,7 @@
       <c r="A445" s="4" t="s">
         <v>2716</v>
       </c>
-      <c r="B445" s="5" t="s">
+      <c r="B445" s="6" t="s">
         <v>2662</v>
       </c>
       <c r="C445" s="4" t="s">
@@ -27540,7 +27540,7 @@
       <c r="A446" s="4" t="s">
         <v>2722</v>
       </c>
-      <c r="B446" s="5" t="s">
+      <c r="B446" s="6" t="s">
         <v>2662</v>
       </c>
       <c r="C446" s="4" t="s">
@@ -27582,7 +27582,7 @@
       <c r="A447" s="4" t="s">
         <v>2728</v>
       </c>
-      <c r="B447" s="5" t="s">
+      <c r="B447" s="6" t="s">
         <v>2662</v>
       </c>
       <c r="C447" s="4" t="s">
@@ -27624,7 +27624,7 @@
       <c r="A448" s="4" t="s">
         <v>2734</v>
       </c>
-      <c r="B448" s="5" t="s">
+      <c r="B448" s="6" t="s">
         <v>2662</v>
       </c>
       <c r="C448" s="4" t="s">
@@ -27666,7 +27666,7 @@
       <c r="A449" s="4" t="s">
         <v>2740</v>
       </c>
-      <c r="B449" s="5" t="s">
+      <c r="B449" s="6" t="s">
         <v>2662</v>
       </c>
       <c r="C449" s="4" t="s">
@@ -27708,7 +27708,7 @@
       <c r="A450" s="4" t="s">
         <v>2746</v>
       </c>
-      <c r="B450" s="5" t="s">
+      <c r="B450" s="6" t="s">
         <v>2662</v>
       </c>
       <c r="C450" s="4" t="s">
@@ -27750,7 +27750,7 @@
       <c r="A451" s="4" t="s">
         <v>2752</v>
       </c>
-      <c r="B451" s="5" t="s">
+      <c r="B451" s="6" t="s">
         <v>2753</v>
       </c>
       <c r="C451" s="4" t="s">
@@ -27792,7 +27792,7 @@
       <c r="A452" s="4" t="s">
         <v>2759</v>
       </c>
-      <c r="B452" s="5" t="s">
+      <c r="B452" s="6" t="s">
         <v>2753</v>
       </c>
       <c r="C452" s="4" t="s">
@@ -27834,7 +27834,7 @@
       <c r="A453" s="4" t="s">
         <v>2765</v>
       </c>
-      <c r="B453" s="5" t="s">
+      <c r="B453" s="6" t="s">
         <v>2753</v>
       </c>
       <c r="C453" s="4" t="s">
@@ -27876,7 +27876,7 @@
       <c r="A454" s="4" t="s">
         <v>2771</v>
       </c>
-      <c r="B454" s="5" t="s">
+      <c r="B454" s="6" t="s">
         <v>2753</v>
       </c>
       <c r="C454" s="4" t="s">
@@ -27918,7 +27918,7 @@
       <c r="A455" s="4" t="s">
         <v>2777</v>
       </c>
-      <c r="B455" s="5" t="s">
+      <c r="B455" s="6" t="s">
         <v>2753</v>
       </c>
       <c r="C455" s="4" t="s">
@@ -27960,7 +27960,7 @@
       <c r="A456" s="4" t="s">
         <v>2783</v>
       </c>
-      <c r="B456" s="5" t="s">
+      <c r="B456" s="6" t="s">
         <v>2753</v>
       </c>
       <c r="C456" s="4" t="s">
@@ -28002,7 +28002,7 @@
       <c r="A457" s="4" t="s">
         <v>2789</v>
       </c>
-      <c r="B457" s="5" t="s">
+      <c r="B457" s="6" t="s">
         <v>2753</v>
       </c>
       <c r="C457" s="4" t="s">
@@ -28044,7 +28044,7 @@
       <c r="A458" s="4" t="s">
         <v>2795</v>
       </c>
-      <c r="B458" s="5" t="s">
+      <c r="B458" s="6" t="s">
         <v>2753</v>
       </c>
       <c r="C458" s="4" t="s">
@@ -28086,7 +28086,7 @@
       <c r="A459" s="4" t="s">
         <v>2801</v>
       </c>
-      <c r="B459" s="5" t="s">
+      <c r="B459" s="6" t="s">
         <v>2753</v>
       </c>
       <c r="C459" s="4" t="s">
@@ -28128,7 +28128,7 @@
       <c r="A460" s="4" t="s">
         <v>2807</v>
       </c>
-      <c r="B460" s="5" t="s">
+      <c r="B460" s="6" t="s">
         <v>2753</v>
       </c>
       <c r="C460" s="4" t="s">
@@ -28170,7 +28170,7 @@
       <c r="A461" s="4" t="s">
         <v>2813</v>
       </c>
-      <c r="B461" s="5" t="s">
+      <c r="B461" s="6" t="s">
         <v>2753</v>
       </c>
       <c r="C461" s="4" t="s">
@@ -28212,7 +28212,7 @@
       <c r="A462" s="4" t="s">
         <v>2819</v>
       </c>
-      <c r="B462" s="5" t="s">
+      <c r="B462" s="6" t="s">
         <v>2753</v>
       </c>
       <c r="C462" s="4" t="s">
@@ -28254,7 +28254,7 @@
       <c r="A463" s="4" t="s">
         <v>2825</v>
       </c>
-      <c r="B463" s="5" t="s">
+      <c r="B463" s="6" t="s">
         <v>2753</v>
       </c>
       <c r="C463" s="4" t="s">
@@ -28296,7 +28296,7 @@
       <c r="A464" s="4" t="s">
         <v>2831</v>
       </c>
-      <c r="B464" s="5" t="s">
+      <c r="B464" s="6" t="s">
         <v>2753</v>
       </c>
       <c r="C464" s="4" t="s">
@@ -28338,7 +28338,7 @@
       <c r="A465" s="4" t="s">
         <v>2837</v>
       </c>
-      <c r="B465" s="5" t="s">
+      <c r="B465" s="6" t="s">
         <v>2753</v>
       </c>
       <c r="C465" s="4" t="s">
